--- a/样板间投顾组合/样板间投顾组合监控模板-20260716调仓.xlsx
+++ b/样板间投顾组合/样板间投顾组合监控模板-20260716调仓.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" firstSheet="2" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="实盘持仓配置" sheetId="1" r:id="rId1"/>
@@ -1157,39 +1157,6 @@
     <t>宏利领先中小盘混合</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Linux Libertine G"/>
-        <family val="2"/>
-      </rPr>
-      <t>组合净值（实盘）</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Linux Libertine G"/>
-        <family val="2"/>
-      </rPr>
-      <t>各组合自起始日买入持有逐日计算</t>
-    </r>
-  </si>
-  <si>
     <t>组合 产业趋势</t>
   </si>
   <si>
@@ -4518,6 +4485,31 @@
       <t>C</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>组合净值</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="39" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -4535,7 +4527,7 @@
     <numFmt numFmtId="184" formatCode="0.00000000%"/>
     <numFmt numFmtId="185" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="10"/>
       <name val="Linux Libertine G"/>
@@ -4555,7 +4547,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Linux Libertine G"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -4812,6 +4804,14 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -5029,21 +5029,21 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5176,6 +5176,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -5206,7 +5207,7 @@
               <c:f>'看板-产业趋势'!_ChartDates</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46195</c:v>
                 </c:pt>
@@ -5293,6 +5294,27 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5302,7 +5324,7 @@
               <c:f>'看板-产业趋势'!_ChartValues</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -5388,7 +5410,28 @@
                   <c:v>0.75909621549224715</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.75906478407377931</c:v>
+                  <c:v>0.70197151091105148</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.72624632001160483</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.6962683081309522</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.74614458366388403</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.77896150349312188</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.79001227829138299</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.81131379383137059</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.81121594075829673</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5404,11 +5447,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-478108112"/>
-        <c:axId val="-478120624"/>
+        <c:axId val="340569632"/>
+        <c:axId val="340573440"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="-478108112"/>
+        <c:axId val="340569632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="46195"/>
@@ -5419,7 +5462,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-478120624"/>
+        <c:crossAx val="340573440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -5427,7 +5470,7 @@
         <c:majorTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="-478120624"/>
+        <c:axId val="340573440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5438,7 +5481,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-478108112"/>
+        <c:crossAx val="340569632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5509,7 +5552,7 @@
               <c:f>'看板-产业趋势基石'!_ChartDates</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46191</c:v>
                 </c:pt>
@@ -5599,6 +5642,27 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5608,7 +5672,7 @@
               <c:f>'看板-产业趋势基石'!_ChartValues</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -5697,7 +5761,28 @@
                   <c:v>0.77644814898918524</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.77642246795265424</c:v>
+                  <c:v>0.71793541970282437</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.74282726366224527</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.71222410579163131</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.76336947663905597</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.79692340056760913</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.80826511012075786</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.83008467669236141</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.83000523901410417</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5713,11 +5798,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-478120080"/>
-        <c:axId val="-478119536"/>
+        <c:axId val="340563104"/>
+        <c:axId val="340563648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="-478120080"/>
+        <c:axId val="340563104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="46191"/>
@@ -5728,7 +5813,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-478119536"/>
+        <c:crossAx val="340563648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -5736,7 +5821,7 @@
         <c:majorTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="-478119536"/>
+        <c:axId val="340563648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5747,7 +5832,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-478120080"/>
+        <c:crossAx val="340563104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5795,7 +5880,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -5826,7 +5910,7 @@
               <c:f>'看板-产业趋势2号'!_ChartDates</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46196</c:v>
                 </c:pt>
@@ -5910,6 +5994,27 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5919,7 +6024,7 @@
               <c:f>'看板-产业趋势2号'!_ChartValues</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -6002,7 +6107,28 @@
                   <c:v>0.80514197361881068</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.80510863561266288</c:v>
+                  <c:v>0.74787436802830576</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.77133249538722459</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.73222495499610107</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.77918745072942763</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.81627637308703827</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.82647704725758364</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.84783459383647197</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.84773216402641249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6018,11 +6144,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-165236016"/>
-        <c:axId val="-165251248"/>
+        <c:axId val="340562560"/>
+        <c:axId val="340570720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="-165236016"/>
+        <c:axId val="340562560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="46196"/>
@@ -6033,7 +6159,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-165251248"/>
+        <c:crossAx val="340570720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -6041,7 +6167,7 @@
         <c:majorTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="-165251248"/>
+        <c:axId val="340570720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6052,7 +6178,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-165236016"/>
+        <c:crossAx val="340562560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6127,7 +6253,7 @@
               <c:f>'看板-10-90'!_ChartDates</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46197</c:v>
                 </c:pt>
@@ -6208,6 +6334,27 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6217,7 +6364,7 @@
               <c:f>'看板-10-90'!_ChartValues</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -6297,7 +6444,28 @@
                   <c:v>0.98026906419805526</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.98024749268353539</c:v>
+                  <c:v>0.9761214913199201</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.97927214944896834</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.97645840479381407</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.9809307866654694</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.98575511215025358</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.98807991531029082</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.99118243223928182</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.99111988587101385</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6313,11 +6481,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-165250160"/>
-        <c:axId val="-165250704"/>
+        <c:axId val="340566368"/>
+        <c:axId val="340577248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="-165250160"/>
+        <c:axId val="340566368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="46197"/>
@@ -6328,7 +6496,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-165250704"/>
+        <c:crossAx val="340577248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -6336,7 +6504,7 @@
         <c:majorTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="-165250704"/>
+        <c:axId val="340577248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6347,7 +6515,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-165250160"/>
+        <c:crossAx val="340566368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6422,7 +6590,7 @@
               <c:f>'看板-10-90基石'!_ChartDates</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46191</c:v>
                 </c:pt>
@@ -6512,6 +6680,27 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6521,7 +6710,7 @@
               <c:f>'看板-10-90基石'!_ChartValues</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -6610,7 +6799,28 @@
                   <c:v>0.9782589797667538</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.97824554543694497</c:v>
+                  <c:v>0.97390321005734459</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.97719837247619623</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.97483599855662972</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.97968557339554074</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.98435681211622128</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.98673128064354332</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.98991772635449637</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.9898798291506663</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6626,11 +6836,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-28085344"/>
-        <c:axId val="-28083712"/>
+        <c:axId val="340564736"/>
+        <c:axId val="340565280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="-28085344"/>
+        <c:axId val="340564736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="46191"/>
@@ -6641,7 +6851,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-28083712"/>
+        <c:crossAx val="340565280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -6649,7 +6859,7 @@
         <c:majorTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="-28083712"/>
+        <c:axId val="340565280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6660,7 +6870,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-28085344"/>
+        <c:crossAx val="340564736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6734,7 +6944,7 @@
               <c:f>'看板-30-70'!_ChartDates</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46197</c:v>
                 </c:pt>
@@ -6815,6 +7025,27 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6824,7 +7055,7 @@
               <c:f>'看板-30-70'!_ChartValues</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -6904,7 +7135,28 @@
                   <c:v>0.93860410362572089</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.93857305927806578</c:v>
+                  <c:v>0.92445284206535505</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.93264826644668219</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.92408565948164412</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.93652463834702993</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.94971573113282171</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.95513401394071007</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.96277386059938297</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.96268377880038403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6920,11 +7172,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-28084256"/>
-        <c:axId val="-686804032"/>
+        <c:axId val="340575616"/>
+        <c:axId val="340569088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="-28084256"/>
+        <c:axId val="340575616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="46197"/>
@@ -6935,7 +7187,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-686804032"/>
+        <c:crossAx val="340569088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -6943,7 +7195,7 @@
         <c:majorTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="-686804032"/>
+        <c:axId val="340569088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6954,7 +7206,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-28084256"/>
+        <c:crossAx val="340575616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7016,8 +7268,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>91800</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1069700</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>136080</xdr:rowOff>
     </xdr:to>
@@ -7382,9 +7634,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA11"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" customWidth="1"/>
     <col min="2" max="24" width="12.08984375" customWidth="1"/>
     <col min="25" max="26" width="9.90625" customWidth="1"/>
     <col min="27" max="27" width="13.1796875" customWidth="1"/>
@@ -8079,269 +8331,263 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G35"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="2.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
     <col min="4" max="4" width="19.26953125" customWidth="1"/>
     <col min="5" max="5" width="20.81640625" customWidth="1"/>
-    <col min="6" max="6" width="16.54296875" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" customWidth="1"/>
     <col min="8" max="8" width="2.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" customHeight="1">
-      <c r="B2" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="B2" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="2:7" ht="14.25" customHeight="1">
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="58" t="str">
         <f>"买入持有 · 已扣年化费率 "&amp;TEXT(实盘持仓配置!$Z$9,"0.0%")&amp;"（折每日计入净值）"</f>
         <v>买入持有 · 已扣年化费率 1.2%（折每日计入净值）</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62" t="str">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59" t="str">
         <f>"净值日期："&amp;TEXT(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),"yyyy-mm-dd")</f>
-        <v>净值日期：2026-07-30</v>
-      </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+        <v>净值日期：2026-08-10</v>
+      </c>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="5" spans="2:7" ht="14">
-      <c r="B5" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
     </row>
     <row r="6" spans="2:7" ht="13">
       <c r="B6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="27.75" customHeight="1">
       <c r="B7" s="27">
         <f>LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)</f>
-        <v>0.93857305927806578</v>
+        <v>0.96268377880038403</v>
       </c>
       <c r="C7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59))/1-1</f>
-        <v>-6.142694072193422E-2</v>
+        <v>-3.7316221199615973E-2</v>
       </c>
       <c r="D7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$R$5:$R$59),1))-1</f>
-        <v>-0.44570444209789639</v>
+        <v>-0.24337597110807752</v>
       </c>
       <c r="E7" s="29">
         <f>STDEV(实盘组合净值!$R$5:$R$59)*SQRT(说明!$C$17)</f>
-        <v>0.16431075200680939</v>
+        <v>0.16870092968727246</v>
       </c>
       <c r="F7" s="28">
         <f>MIN(实盘组合净值!$S$5:$S$59)</f>
-        <v>-7.5014031487720345E-2</v>
+        <v>-8.3940733765942466E-2</v>
       </c>
       <c r="G7" s="30">
         <f>(((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$R$5:$R$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$R$5:$R$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$R$5:$R$59)*SQRT(说明!$C$17)))</f>
-        <v>-2.7125701553567563</v>
+        <v>-1.4426474801249354</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="14">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
     </row>
     <row r="10" spans="2:7" ht="13.5" customHeight="1">
       <c r="B10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="F10" s="62"/>
+      <c r="G10" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="22.5" customHeight="1">
       <c r="B11" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59))/(1)-1,"")</f>
-        <v>-6.142694072193422E-2</v>
+        <v>-3.7316221199615973E-2</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/(1))^(说明!$C$17/COUNT(实盘组合净值!$R$5:$R$59))-1,"")</f>
-        <v>-0.44570444209789639</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="57"/>
+        <v>-0.24337597110807752</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="61"/>
       <c r="G11" s="32">
         <f>MIN(实盘组合净值!$S$5:$S$59)</f>
-        <v>-7.5014031487720345E-2</v>
+        <v>-8.3940733765942466E-2</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="22.5" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59))/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1))-1,"")</f>
-        <v>-6.142694072193422E-2</v>
+        <v>-3.7316221199615973E-2</v>
       </c>
       <c r="D12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(DATE(2026,1,1))),1))-1,"")</f>
-        <v>-0.40033429554543953</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="F12" s="57"/>
+        <v>-0.22021626987305187</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="34">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),ROW(实盘组合净值!$Q$5:$Q$59)))-(LOOKUP(2,1/(实盘组合净值!$S$5:$S$59=0),ROW(实盘组合净值!$S$5:$S$59))),"")</f>
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="22.5" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1))-1,"")</f>
-        <v>-6.142694072193422E-2</v>
+        <v>-3.7316221199615973E-2</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3))),1))-1,"")</f>
-        <v>-0.40033429554543953</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="57"/>
+        <v>-0.22021626987305187</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="35">
         <f>COUNTIF(实盘组合净值!$R$5:$R$59,"&gt;0")/MAX(COUNT(实盘组合净值!$R$5:$R$59),1)</f>
-        <v>0.30769230769230771</v>
+        <v>0.39393939393939392</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="22.5" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1))-1,"")</f>
-        <v>-6.142694072193422E-2</v>
+        <v>-3.7316221199615973E-2</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6))),1))-1,"")</f>
-        <v>-0.40033429554543953</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="57"/>
+        <v>-0.22021626987305187</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="61"/>
       <c r="G14" s="32">
         <f>STDEV(实盘组合净值!$R$5:$R$59)*SQRT(说明!$C$17)</f>
-        <v>0.16431075200680939</v>
+        <v>0.16870092968727246</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="22.5" customHeight="1">
       <c r="B15" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1))-1,"")</f>
-        <v>-6.142694072193422E-2</v>
+        <v>-3.7316221199615973E-2</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$Q$5:$Q$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12))),1))-1,"")</f>
-        <v>-0.40033429554543953</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="57"/>
+        <v>-0.22021626987305187</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="61"/>
       <c r="G15" s="36">
         <f>(((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$R$5:$R$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$R$5:$R$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$R$5:$R$59)*SQRT(说明!$C$17)))</f>
-        <v>-2.7125701553567563</v>
+        <v>-1.4426474801249354</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="22.5" customHeight="1">
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
-      <c r="E16" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="F16" s="57"/>
+      <c r="E16" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="61"/>
       <c r="G16" s="36">
         <f>IFERROR(((LOOKUP(2,1/(实盘组合净值!$Q$5:$Q$59&lt;&gt;""),实盘组合净值!$Q$5:$Q$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$R$5:$R$59),1))-1)/ABS(MIN(实盘组合净值!$S$5:$S$59)),"")</f>
-        <v>-5.9416142987976501</v>
+        <v>-2.8993786471619241</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14">
-      <c r="B18" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="35" spans="2:2" ht="14.25" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="B18:G18"/>
@@ -8350,6 +8596,12 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8361,34 +8613,34 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H19"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="2.1796875" customWidth="1"/>
-    <col min="2" max="2" width="28.54296875" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
     <col min="3" max="8" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="22.5" customHeight="1">
       <c r="B2" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="14.25" customHeight="1">
       <c r="B3" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="16.5" customHeight="1">
       <c r="B6" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="63" t="s">
         <v>173</v>
-      </c>
-      <c r="C6" s="63" t="s">
-        <v>174</v>
       </c>
       <c r="D6" s="63"/>
       <c r="E6" s="63"/>
@@ -8398,10 +8650,10 @@
     </row>
     <row r="7" spans="2:8" ht="25.5" customHeight="1">
       <c r="B7" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="63" t="s">
         <v>175</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>176</v>
       </c>
       <c r="D7" s="63"/>
       <c r="E7" s="63"/>
@@ -8411,10 +8663,10 @@
     </row>
     <row r="8" spans="2:8" ht="16.5" customHeight="1">
       <c r="B8" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="63" t="s">
         <v>177</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>178</v>
       </c>
       <c r="D8" s="63"/>
       <c r="E8" s="63"/>
@@ -8424,10 +8676,10 @@
     </row>
     <row r="9" spans="2:8" ht="27.75" customHeight="1">
       <c r="B9" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="64" t="s">
         <v>179</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>180</v>
       </c>
       <c r="D9" s="64"/>
       <c r="E9" s="64"/>
@@ -8446,7 +8698,7 @@
     </row>
     <row r="11" spans="2:8" ht="16.5" customHeight="1">
       <c r="B11" s="39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -8457,10 +8709,10 @@
     </row>
     <row r="12" spans="2:8" ht="16.5" customHeight="1">
       <c r="B12" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="63" t="s">
         <v>182</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>183</v>
       </c>
       <c r="D12" s="63"/>
       <c r="E12" s="63"/>
@@ -8470,10 +8722,10 @@
     </row>
     <row r="13" spans="2:8" ht="16.5" customHeight="1">
       <c r="B13" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="63" t="s">
         <v>184</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>185</v>
       </c>
       <c r="D13" s="63"/>
       <c r="E13" s="63"/>
@@ -8483,10 +8735,10 @@
     </row>
     <row r="14" spans="2:8" ht="16.5" customHeight="1">
       <c r="B14" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="63" t="s">
         <v>186</v>
-      </c>
-      <c r="C14" s="63" t="s">
-        <v>187</v>
       </c>
       <c r="D14" s="63"/>
       <c r="E14" s="63"/>
@@ -8496,15 +8748,15 @@
     </row>
     <row r="15" spans="2:8" ht="14.25" customHeight="1">
       <c r="B15" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="41" t="s">
         <v>188</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="13">
       <c r="B16" s="40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="44">
         <v>0</v>
@@ -8512,7 +8764,7 @@
     </row>
     <row r="17" spans="2:3" ht="13">
       <c r="B17" s="40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="45">
         <v>242</v>
@@ -8520,15 +8772,15 @@
     </row>
     <row r="18" spans="2:3" ht="14.25" customHeight="1">
       <c r="B18" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="41" t="s">
         <v>192</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14.25" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -8550,59 +8802,59 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="24.08984375" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" customWidth="1"/>
     <col min="3" max="4" width="18.6328125" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
     <col min="7" max="7" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.5">
       <c r="A1" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1" s="47" t="s">
         <v>195</v>
-      </c>
-      <c r="F1" s="47" t="s">
-        <v>196</v>
       </c>
       <c r="G1">
         <f>COUNT('实盘净值数据(iFinD公式)'!$B$5:$B$60)</f>
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.5">
       <c r="A2" s="46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2" s="48">
         <f>INDEX('实盘净值数据(iFinD公式)'!$A$5:$A$60,$G$1)</f>
-        <v>46233</v>
+        <v>46244</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2">
         <f>SUMPRODUCT(实盘持仓配置!$B$4:$X$4,INDEX('实盘净值数据(iFinD公式)'!$B$5:$X$60,$G$1,0)/'实盘净值数据(iFinD公式)'!$B$6:$X$6)</f>
-        <v>0.75374099067021627</v>
+        <v>0.81128993671706628</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14">
       <c r="F3" s="47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3">
         <f>SUMPRODUCT(实盘持仓配置!$B$5:$X$5,INDEX('实盘净值数据(iFinD公式)'!$B$5:$X$60,$G$1,0)/'实盘净值数据(iFinD公式)'!$B$5:$X$5)</f>
-        <v>0.77095044726907802</v>
+        <v>0.82992864947389233</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.5">
       <c r="F4" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G4">
         <f>SUMPRODUCT(实盘持仓配置!$B$6:$X$6,INDEX('实盘净值数据(iFinD公式)'!$B$5:$X$60,$G$1,0)/'实盘净值数据(iFinD公式)'!$B$7:$X$7)</f>
-        <v>0.79990869446746837</v>
+        <v>0.84803174942787274</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.5">
@@ -8613,15 +8865,15 @@
         <v>28</v>
       </c>
       <c r="C5" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="50" t="s">
         <v>201</v>
-      </c>
-      <c r="D5" s="50" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.5">
       <c r="A6" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B6" s="51" t="s">
         <v>47</v>
@@ -8632,12 +8884,12 @@
       </c>
       <c r="D6" s="52">
         <f>实盘持仓配置!T$4*INDEX('实盘净值数据(iFinD公式)'!T$5:T$60,$G$1)/'实盘净值数据(iFinD公式)'!T$6/$G$2</f>
-        <v>0.13297440928754389</v>
+        <v>0.12958183482776112</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.5">
       <c r="A7" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B7" s="51" t="s">
         <v>34</v>
@@ -8648,12 +8900,12 @@
       </c>
       <c r="D7" s="52">
         <f>实盘持仓配置!G$4*INDEX('实盘净值数据(iFinD公式)'!G$5:G$60,$G$1)/'实盘净值数据(iFinD公式)'!G$6/$G$2</f>
-        <v>9.7841551616394573E-2</v>
+        <v>9.9345968164977996E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.5">
       <c r="A8" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>31</v>
@@ -8664,12 +8916,12 @@
       </c>
       <c r="D8" s="52">
         <f>实盘持仓配置!D$4*INDEX('实盘净值数据(iFinD公式)'!D$5:D$60,$G$1)/'实盘净值数据(iFinD公式)'!D$6/$G$2</f>
-        <v>0.16605037092430486</v>
+        <v>0.16860239822001988</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.5">
       <c r="A9" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B9" s="51" t="s">
         <v>44</v>
@@ -8680,12 +8932,12 @@
       </c>
       <c r="D9" s="52">
         <f>实盘持仓配置!Q$4*INDEX('实盘净值数据(iFinD公式)'!Q$5:Q$60,$G$1)/'实盘净值数据(iFinD公式)'!Q$6/$G$2</f>
-        <v>0.1692976693533452</v>
+        <v>0.17347715785334891</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.5">
       <c r="A10" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>43</v>
@@ -8696,12 +8948,12 @@
       </c>
       <c r="D10" s="52">
         <f>实盘持仓配置!P$4*INDEX('实盘净值数据(iFinD公式)'!P$5:P$60,$G$1)/'实盘净值数据(iFinD公式)'!P$6/$G$2</f>
-        <v>0.15085133912268311</v>
+        <v>0.16000048427017474</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.5">
       <c r="A11" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>37</v>
@@ -8712,12 +8964,12 @@
       </c>
       <c r="D11" s="52">
         <f>实盘持仓配置!J$4*INDEX('实盘净值数据(iFinD公式)'!J$5:J$60,$G$1)/'实盘净值数据(iFinD公式)'!J$6/$G$2</f>
-        <v>0.25641661210415179</v>
+        <v>0.24429958789013034</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.5">
       <c r="A12" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="51" t="s">
         <v>30</v>
@@ -8728,7 +8980,7 @@
       </c>
       <c r="D12" s="52">
         <f>实盘持仓配置!C$4*INDEX('实盘净值数据(iFinD公式)'!C$5:C$60,$G$1)/'实盘净值数据(iFinD公式)'!C$6/$G$2</f>
-        <v>2.6568047591576587E-2</v>
+        <v>2.4692568773587074E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.5">
@@ -8746,7 +8998,7 @@
     </row>
     <row r="15" spans="1:7" ht="14.5">
       <c r="A15" s="46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.5">
@@ -8757,15 +9009,15 @@
         <v>28</v>
       </c>
       <c r="C16" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="50" t="s">
         <v>201</v>
-      </c>
-      <c r="D16" s="50" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.5">
       <c r="A17" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>47</v>
@@ -8776,12 +9028,12 @@
       </c>
       <c r="D17" s="52">
         <f>实盘持仓配置!T$5*INDEX('实盘净值数据(iFinD公式)'!T$5:T$60,$G$1)/'实盘净值数据(iFinD公式)'!T$5/$G$3</f>
-        <v>0.13363886894430554</v>
+        <v>0.13021125040589127</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.5">
       <c r="A18" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B18" s="51" t="s">
         <v>34</v>
@@ -8792,12 +9044,12 @@
       </c>
       <c r="D18" s="52">
         <f>实盘持仓配置!G$5*INDEX('实盘净值数据(iFinD公式)'!G$5:G$60,$G$1)/'实盘净值数据(iFinD公式)'!G$5/$G$3</f>
-        <v>9.7267165947724749E-2</v>
+        <v>9.8749030389657988E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.5">
       <c r="A19" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="51" t="s">
         <v>31</v>
@@ -8808,12 +9060,12 @@
       </c>
       <c r="D19" s="52">
         <f>实盘持仓配置!D$5*INDEX('实盘净值数据(iFinD公式)'!D$5:D$60,$G$1)/'实盘净值数据(iFinD公式)'!D$5/$G$3</f>
-        <v>0.16761949928471867</v>
+        <v>0.17017199857798429</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.5">
       <c r="A20" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>44</v>
@@ -8824,12 +9076,12 @@
       </c>
       <c r="D20" s="52">
         <f>实盘持仓配置!Q$5*INDEX('实盘净值数据(iFinD公式)'!Q$5:Q$60,$G$1)/'实盘净值数据(iFinD公式)'!Q$5/$G$3</f>
-        <v>0.17009950710328164</v>
+        <v>0.17427457680083983</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.5">
       <c r="A21" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>43</v>
@@ -8840,12 +9092,12 @@
       </c>
       <c r="D21" s="52">
         <f>实盘持仓配置!P$5*INDEX('实盘净值数据(iFinD公式)'!P$5:P$60,$G$1)/'实盘净值数据(iFinD公式)'!P$5/$G$3</f>
-        <v>0.15076572003165334</v>
+        <v>0.15988745739473806</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.5">
       <c r="A22" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="51" t="s">
         <v>37</v>
@@ -8856,12 +9108,12 @@
       </c>
       <c r="D22" s="52">
         <f>实盘持仓配置!J$5*INDEX('实盘净值数据(iFinD公式)'!J$5:J$60,$G$1)/'实盘净值数据(iFinD公式)'!J$5/$G$3</f>
-        <v>0.25463066660510131</v>
+        <v>0.24256433542655295</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.5">
       <c r="A23" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" s="51" t="s">
         <v>30</v>
@@ -8872,7 +9124,7 @@
       </c>
       <c r="D23" s="52">
         <f>实盘持仓配置!C$5*INDEX('实盘净值数据(iFinD公式)'!C$5:C$60,$G$1)/'实盘净值数据(iFinD公式)'!C$5/$G$3</f>
-        <v>2.5978572083214715E-2</v>
+        <v>2.4141351004335544E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.5">
@@ -8890,7 +9142,7 @@
     </row>
     <row r="26" spans="1:4" ht="14.5">
       <c r="A26" s="46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.5">
@@ -8901,15 +9153,15 @@
         <v>28</v>
       </c>
       <c r="C27" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="50" t="s">
         <v>201</v>
-      </c>
-      <c r="D27" s="50" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14.5">
       <c r="A28" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>48</v>
@@ -8920,12 +9172,12 @@
       </c>
       <c r="D28" s="52">
         <f>实盘持仓配置!U$6*INDEX('实盘净值数据(iFinD公式)'!U$5:U$60,$G$1)/'实盘净值数据(iFinD公式)'!U$7/$G$4</f>
-        <v>0.12530486590334339</v>
+        <v>0.12397013568753085</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="14.5">
       <c r="A29" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="51" t="s">
         <v>35</v>
@@ -8936,12 +9188,12 @@
       </c>
       <c r="D29" s="52">
         <f>实盘持仓配置!H$6*INDEX('实盘净值数据(iFinD公式)'!H$5:H$60,$G$1)/'实盘净值数据(iFinD公式)'!H$7/$G$4</f>
-        <v>9.4868744698187499E-2</v>
+        <v>9.7791031618182561E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.5">
       <c r="A30" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>46</v>
@@ -8952,12 +9204,12 @@
       </c>
       <c r="D30" s="52">
         <f>实盘持仓配置!S$6*INDEX('实盘净值数据(iFinD公式)'!S$5:S$60,$G$1)/'实盘净值数据(iFinD公式)'!S$7/$G$4</f>
-        <v>0.16328738103622661</v>
+        <v>0.16829097623050321</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.5">
       <c r="A31" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" s="51" t="s">
         <v>45</v>
@@ -8968,7 +9220,7 @@
       </c>
       <c r="D31" s="52">
         <f>实盘持仓配置!R$6*INDEX('实盘净值数据(iFinD公式)'!R$5:R$60,$G$1)/'实盘净值数据(iFinD公式)'!R$7/$G$4</f>
-        <v>0.16323206258152059</v>
+        <v>0.16979112531001098</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14">
@@ -8984,12 +9236,12 @@
       </c>
       <c r="D32" s="52">
         <f>实盘持仓配置!I$6*INDEX('实盘净值数据(iFinD公式)'!I$5:I$60,$G$1)/'实盘净值数据(iFinD公式)'!I$7/$G$4</f>
-        <v>0.1884655425881466</v>
+        <v>0.18458187271052659</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="14.5">
       <c r="A33" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="51" t="s">
         <v>38</v>
@@ -9000,12 +9252,12 @@
       </c>
       <c r="D33" s="52">
         <f>实盘持仓配置!K$6*INDEX('实盘净值数据(iFinD公式)'!K$5:K$60,$G$1)/'实盘净值数据(iFinD公式)'!K$7/$G$4</f>
-        <v>0.23980775313187419</v>
+        <v>0.23195305406597924</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="14.5">
       <c r="A34" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B34" s="51" t="s">
         <v>30</v>
@@ -9016,7 +9268,7 @@
       </c>
       <c r="D34" s="52">
         <f>实盘持仓配置!C$6*INDEX('实盘净值数据(iFinD公式)'!C$5:C$60,$G$1)/'实盘净值数据(iFinD公式)'!C$7/$G$4</f>
-        <v>2.5033650060701115E-2</v>
+        <v>2.3621804377266582E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="14.5">
@@ -9047,7 +9299,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y60"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
   </cols>
@@ -9063,7 +9315,7 @@
     <row r="2" spans="1:25" ht="14">
       <c r="A2" s="11">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="24.75" customHeight="1">
@@ -9168,7 +9420,7 @@
     </row>
     <row r="4" spans="1:25" ht="51.75" customHeight="1">
       <c r="A4" s="1" t="str">
-        <f ca="1">[1]!HX_AutoDate(1,"2026-06-18",A2,-1,-1,0,0,0,0,0,"SSE",30,0)</f>
+        <f ca="1">[1]!HX_AutoDate(1,"2026-06-18",A2,-1,-1,0,0,0,0,0,"SSE",37,0)</f>
         <v>日期</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -12179,792 +12431,806 @@
       </c>
       <c r="B34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A34))</f>
-        <v>3.0528</v>
+        <v>3.0495000000000001</v>
       </c>
       <c r="C34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A34))</f>
-        <v>1.3191353025999999</v>
+        <v>1.3191793221000001</v>
       </c>
       <c r="D34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A34))</f>
-        <v>4.1230000000000002</v>
+        <v>3.81</v>
       </c>
       <c r="E34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A34))</f>
-        <v>1.8154999999999999</v>
+        <v>1.7921</v>
       </c>
       <c r="F34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A34))</f>
-        <v>1.7636000000000001</v>
+        <v>1.7408999999999999</v>
       </c>
       <c r="G34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A34))</f>
-        <v>3.4272999999999998</v>
+        <v>3.1764999999999999</v>
       </c>
       <c r="H34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A34))</f>
-        <v>3.3538999999999999</v>
+        <v>3.1084999999999998</v>
       </c>
       <c r="I34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A34))</f>
-        <v>2.3229000000000002</v>
+        <v>2.1554000000000002</v>
       </c>
       <c r="J34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A34))</f>
-        <v>3.1309</v>
+        <v>2.9123000000000001</v>
       </c>
       <c r="K34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A34))</f>
-        <v>3.1019000000000001</v>
+        <v>2.8853</v>
       </c>
       <c r="L34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A34))</f>
-        <v>1.4198999999999999</v>
+        <v>1.3827</v>
       </c>
       <c r="M34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A34))</f>
-        <v>1.4007000000000001</v>
+        <v>1.3638999999999999</v>
       </c>
       <c r="N34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A34))</f>
-        <v>1.4406000000000001</v>
+        <v>1.3997999999999999</v>
       </c>
       <c r="O34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A34))</f>
-        <v>1.4046000000000001</v>
+        <v>1.3648</v>
       </c>
       <c r="P34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A34))</f>
-        <v>2.2269000000000001</v>
+        <v>2.0009999999999999</v>
       </c>
       <c r="Q34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A34))</f>
-        <v>3.0274999999999999</v>
+        <v>2.7465000000000002</v>
       </c>
       <c r="R34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A34))</f>
-        <v>2.9632000000000001</v>
+        <v>2.6880999999999999</v>
       </c>
       <c r="S34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A34))</f>
-        <v>4.08</v>
+        <v>3.77</v>
       </c>
       <c r="T34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A34))</f>
-        <v>2.8022</v>
+        <v>2.6145999999999998</v>
       </c>
       <c r="U34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A34))</f>
-        <v>2.7871000000000001</v>
+        <v>2.6004999999999998</v>
       </c>
       <c r="V34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A34))</f>
-        <v>1.7188000000000001</v>
+        <v>1.6605000000000001</v>
       </c>
       <c r="W34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A34))</f>
-        <v>1.7016</v>
+        <v>1.6437999999999999</v>
       </c>
       <c r="X34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A34))</f>
-        <v>1.7935000000000001</v>
+        <v>1.7955000000000001</v>
       </c>
       <c r="Y34" s="13">
         <f>IF($A34="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A34))</f>
-        <v>2.399</v>
+        <v>2.222</v>
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="13" t="str">
+      <c r="A35" s="8">
+        <v>46234</v>
+      </c>
+      <c r="B35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="C35" s="13" t="str">
+        <v>3.0642999999999998</v>
+      </c>
+      <c r="C35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="D35" s="13" t="str">
+        <v>1.3192249393</v>
+      </c>
+      <c r="D35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="13" t="str">
+        <v>3.9750000000000001</v>
+      </c>
+      <c r="E35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="F35" s="13" t="str">
+        <v>1.8093999999999999</v>
+      </c>
+      <c r="F35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="G35" s="13" t="str">
+        <v>1.7577</v>
+      </c>
+      <c r="G35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="H35" s="13" t="str">
+        <v>3.3206000000000002</v>
+      </c>
+      <c r="H35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="I35" s="13" t="str">
+        <v>3.2494999999999998</v>
+      </c>
+      <c r="I35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="13" t="str">
+        <v>2.2254999999999998</v>
+      </c>
+      <c r="J35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="13" t="str">
+        <v>2.9811999999999999</v>
+      </c>
+      <c r="K35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="L35" s="13" t="str">
+        <v>2.9535999999999998</v>
+      </c>
+      <c r="L35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="M35" s="13" t="str">
+        <v>1.4158999999999999</v>
+      </c>
+      <c r="M35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="N35" s="13" t="str">
+        <v>1.3967000000000001</v>
+      </c>
+      <c r="N35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="O35" s="13" t="str">
+        <v>1.4318</v>
+      </c>
+      <c r="O35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="P35" s="13" t="str">
+        <v>1.3959999999999999</v>
+      </c>
+      <c r="P35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="Q35" s="13" t="str">
+        <v>2.1139000000000001</v>
+      </c>
+      <c r="Q35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="R35" s="13" t="str">
+        <v>2.8824000000000001</v>
+      </c>
+      <c r="R35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="S35" s="13" t="str">
+        <v>2.8210999999999999</v>
+      </c>
+      <c r="S35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="T35" s="13" t="str">
+        <v>3.9329999999999998</v>
+      </c>
+      <c r="T35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="U35" s="13" t="str">
+        <v>2.6698</v>
+      </c>
+      <c r="U35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="V35" s="13" t="str">
+        <v>2.6554000000000002</v>
+      </c>
+      <c r="V35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="W35" s="13" t="str">
+        <v>1.7142999999999999</v>
+      </c>
+      <c r="W35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="X35" s="13" t="str">
+        <v>1.6970000000000001</v>
+      </c>
+      <c r="X35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A35))</f>
-        <v/>
-      </c>
-      <c r="Y35" s="13" t="str">
+        <v>1.7963</v>
+      </c>
+      <c r="Y35" s="13">
         <f>IF($A35="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A35))</f>
-        <v/>
+        <v>2.2930000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="13" t="str">
+      <c r="A36" s="8">
+        <v>46237</v>
+      </c>
+      <c r="B36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="C36" s="13" t="str">
+        <v>3.0567000000000002</v>
+      </c>
+      <c r="C36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="D36" s="13" t="str">
+        <v>1.3193583834</v>
+      </c>
+      <c r="D36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="13" t="str">
+        <v>3.923</v>
+      </c>
+      <c r="E36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="F36" s="13" t="str">
+        <v>1.7925</v>
+      </c>
+      <c r="F36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="G36" s="13" t="str">
+        <v>1.7412000000000001</v>
+      </c>
+      <c r="G36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="H36" s="13" t="str">
+        <v>3.3317000000000001</v>
+      </c>
+      <c r="H36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="I36" s="13" t="str">
+        <v>3.2602000000000002</v>
+      </c>
+      <c r="I36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="13" t="str">
+        <v>2.1049000000000002</v>
+      </c>
+      <c r="J36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="13" t="str">
+        <v>2.7321</v>
+      </c>
+      <c r="K36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="L36" s="13" t="str">
+        <v>2.7067000000000001</v>
+      </c>
+      <c r="L36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="M36" s="13" t="str">
+        <v>1.4174</v>
+      </c>
+      <c r="M36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="N36" s="13" t="str">
+        <v>1.3982000000000001</v>
+      </c>
+      <c r="N36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="O36" s="13" t="str">
+        <v>1.4220999999999999</v>
+      </c>
+      <c r="O36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="P36" s="13" t="str">
+        <v>1.3865000000000001</v>
+      </c>
+      <c r="P36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="Q36" s="13" t="str">
+        <v>2.1360000000000001</v>
+      </c>
+      <c r="Q36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="R36" s="13" t="str">
+        <v>2.8574000000000002</v>
+      </c>
+      <c r="R36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="S36" s="13" t="str">
+        <v>2.7965</v>
+      </c>
+      <c r="S36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="T36" s="13" t="str">
+        <v>3.8820000000000001</v>
+      </c>
+      <c r="T36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="U36" s="13" t="str">
+        <v>2.4445000000000001</v>
+      </c>
+      <c r="U36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="V36" s="13" t="str">
+        <v>2.4312999999999998</v>
+      </c>
+      <c r="V36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="W36" s="13" t="str">
+        <v>1.7267999999999999</v>
+      </c>
+      <c r="W36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="X36" s="13" t="str">
+        <v>1.7094</v>
+      </c>
+      <c r="X36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A36))</f>
-        <v/>
-      </c>
-      <c r="Y36" s="13" t="str">
+        <v>1.7967</v>
+      </c>
+      <c r="Y36" s="13">
         <f>IF($A36="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A36))</f>
-        <v/>
+        <v>2.0819999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="13" t="str">
+      <c r="A37" s="8">
+        <v>46238</v>
+      </c>
+      <c r="B37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="C37" s="13" t="str">
+        <v>3.0604</v>
+      </c>
+      <c r="C37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="D37" s="13" t="str">
+        <v>1.3194026215000001</v>
+      </c>
+      <c r="D37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="13" t="str">
+        <v>4.2619999999999996</v>
+      </c>
+      <c r="E37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="F37" s="13" t="str">
+        <v>1.8268</v>
+      </c>
+      <c r="F37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="G37" s="13" t="str">
+        <v>1.7745</v>
+      </c>
+      <c r="G37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="H37" s="13" t="str">
+        <v>3.6164000000000001</v>
+      </c>
+      <c r="H37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="I37" s="13" t="str">
+        <v>3.5388000000000002</v>
+      </c>
+      <c r="I37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="13" t="str">
+        <v>2.2496</v>
+      </c>
+      <c r="J37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="13" t="str">
+        <v>2.8633000000000002</v>
+      </c>
+      <c r="K37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="L37" s="13" t="str">
+        <v>2.8365999999999998</v>
+      </c>
+      <c r="L37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="M37" s="13" t="str">
+        <v>1.4543999999999999</v>
+      </c>
+      <c r="M37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="N37" s="13" t="str">
+        <v>1.4347000000000001</v>
+      </c>
+      <c r="N37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="O37" s="13" t="str">
+        <v>1.4601</v>
+      </c>
+      <c r="O37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="P37" s="13" t="str">
+        <v>1.4235</v>
+      </c>
+      <c r="P37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="Q37" s="13" t="str">
+        <v>2.3923000000000001</v>
+      </c>
+      <c r="Q37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="R37" s="13" t="str">
+        <v>3.1415000000000002</v>
+      </c>
+      <c r="R37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="S37" s="13" t="str">
+        <v>3.0745</v>
+      </c>
+      <c r="S37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="T37" s="13" t="str">
+        <v>4.2169999999999996</v>
+      </c>
+      <c r="T37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="U37" s="13" t="str">
+        <v>2.5649999999999999</v>
+      </c>
+      <c r="U37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="V37" s="13" t="str">
+        <v>2.5510999999999999</v>
+      </c>
+      <c r="V37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="W37" s="13" t="str">
+        <v>1.7741</v>
+      </c>
+      <c r="W37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="X37" s="13" t="str">
+        <v>1.7562</v>
+      </c>
+      <c r="X37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A37))</f>
-        <v/>
-      </c>
-      <c r="Y37" s="13" t="str">
+        <v>1.7972999999999999</v>
+      </c>
+      <c r="Y37" s="13">
         <f>IF($A37="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A37))</f>
-        <v/>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="13" t="str">
+      <c r="A38" s="8">
+        <v>46239</v>
+      </c>
+      <c r="B38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="C38" s="13" t="str">
+        <v>3.13</v>
+      </c>
+      <c r="C38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="D38" s="13" t="str">
+        <v>1.3194468346999999</v>
+      </c>
+      <c r="D38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="13" t="str">
+        <v>4.327</v>
+      </c>
+      <c r="E38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="F38" s="13" t="str">
+        <v>1.8555999999999999</v>
+      </c>
+      <c r="F38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="G38" s="13" t="str">
+        <v>1.8025</v>
+      </c>
+      <c r="G38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="H38" s="13" t="str">
+        <v>3.6436999999999999</v>
+      </c>
+      <c r="H38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="I38" s="13" t="str">
+        <v>3.5653999999999999</v>
+      </c>
+      <c r="I38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="13" t="str">
+        <v>2.3281999999999998</v>
+      </c>
+      <c r="J38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="13" t="str">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="K38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="L38" s="13" t="str">
+        <v>3.0651999999999999</v>
+      </c>
+      <c r="L38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="M38" s="13" t="str">
+        <v>1.4952000000000001</v>
+      </c>
+      <c r="M38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="N38" s="13" t="str">
+        <v>1.4749000000000001</v>
+      </c>
+      <c r="N38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="O38" s="13" t="str">
+        <v>1.5001</v>
+      </c>
+      <c r="O38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="P38" s="13" t="str">
+        <v>1.4624999999999999</v>
+      </c>
+      <c r="P38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="Q38" s="13" t="str">
+        <v>2.4121000000000001</v>
+      </c>
+      <c r="Q38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="R38" s="13" t="str">
+        <v>3.2088000000000001</v>
+      </c>
+      <c r="R38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="S38" s="13" t="str">
+        <v>3.1402999999999999</v>
+      </c>
+      <c r="S38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="T38" s="13" t="str">
+        <v>4.2809999999999997</v>
+      </c>
+      <c r="T38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="U38" s="13" t="str">
+        <v>2.8005</v>
+      </c>
+      <c r="U38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="V38" s="13" t="str">
+        <v>2.7854000000000001</v>
+      </c>
+      <c r="V38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="W38" s="13" t="str">
+        <v>1.8227</v>
+      </c>
+      <c r="W38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="X38" s="13" t="str">
+        <v>1.8043</v>
+      </c>
+      <c r="X38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A38))</f>
-        <v/>
-      </c>
-      <c r="Y38" s="13" t="str">
+        <v>1.7971999999999999</v>
+      </c>
+      <c r="Y38" s="13">
         <f>IF($A38="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A38))</f>
-        <v/>
+        <v>2.3660000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="13" t="str">
+      <c r="A39" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="C39" s="13" t="str">
+        <v>3.2039</v>
+      </c>
+      <c r="C39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="D39" s="13" t="str">
+        <v>1.3194908778000001</v>
+      </c>
+      <c r="D39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="13" t="str">
+        <v>4.3879999999999999</v>
+      </c>
+      <c r="E39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="F39" s="13" t="str">
+        <v>1.8642000000000001</v>
+      </c>
+      <c r="F39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="G39" s="13" t="str">
+        <v>1.8108</v>
+      </c>
+      <c r="G39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="H39" s="13" t="str">
+        <v>3.7075</v>
+      </c>
+      <c r="H39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="I39" s="13" t="str">
+        <v>3.6278999999999999</v>
+      </c>
+      <c r="I39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="13" t="str">
+        <v>2.3582000000000001</v>
+      </c>
+      <c r="J39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="13" t="str">
+        <v>3.1126999999999998</v>
+      </c>
+      <c r="K39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="L39" s="13" t="str">
+        <v>3.0836999999999999</v>
+      </c>
+      <c r="L39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="M39" s="13" t="str">
+        <v>1.5024999999999999</v>
+      </c>
+      <c r="M39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="N39" s="13" t="str">
+        <v>1.482</v>
+      </c>
+      <c r="N39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="O39" s="13" t="str">
+        <v>1.5098</v>
+      </c>
+      <c r="O39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="P39" s="13" t="str">
+        <v>1.4719</v>
+      </c>
+      <c r="P39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="Q39" s="13" t="str">
+        <v>2.4704000000000002</v>
+      </c>
+      <c r="Q39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="R39" s="13" t="str">
+        <v>3.2561</v>
+      </c>
+      <c r="R39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="S39" s="13" t="str">
+        <v>3.1865999999999999</v>
+      </c>
+      <c r="S39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="T39" s="13" t="str">
+        <v>4.3419999999999996</v>
+      </c>
+      <c r="T39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="U39" s="13" t="str">
+        <v>2.8647</v>
+      </c>
+      <c r="U39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="V39" s="13" t="str">
+        <v>2.8492000000000002</v>
+      </c>
+      <c r="V39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="W39" s="13" t="str">
+        <v>1.8452</v>
+      </c>
+      <c r="W39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="X39" s="13" t="str">
+        <v>1.8265</v>
+      </c>
+      <c r="X39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A39))</f>
-        <v/>
-      </c>
-      <c r="Y39" s="13" t="str">
+        <v>1.7974000000000001</v>
+      </c>
+      <c r="Y39" s="13">
         <f>IF($A39="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A39))</f>
-        <v/>
+        <v>2.4020000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="13" t="str">
+      <c r="A40" s="8">
+        <v>46241</v>
+      </c>
+      <c r="B40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="C40" s="13" t="str">
+        <v>3.22</v>
+      </c>
+      <c r="C40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="D40" s="13" t="str">
+        <v>1.3195356482</v>
+      </c>
+      <c r="D40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="E40" s="13" t="str">
+        <v>4.5060000000000002</v>
+      </c>
+      <c r="E40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="F40" s="13" t="str">
+        <v>1.8923000000000001</v>
+      </c>
+      <c r="F40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="G40" s="13" t="str">
+        <v>1.8381000000000001</v>
+      </c>
+      <c r="G40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="H40" s="13" t="str">
+        <v>3.7456999999999998</v>
+      </c>
+      <c r="H40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="I40" s="13" t="str">
+        <v>3.6652</v>
+      </c>
+      <c r="I40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="J40" s="13" t="str">
+        <v>2.4119000000000002</v>
+      </c>
+      <c r="J40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="K40" s="13" t="str">
+        <v>3.2107000000000001</v>
+      </c>
+      <c r="K40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="L40" s="13" t="str">
+        <v>3.1808000000000001</v>
+      </c>
+      <c r="L40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="M40" s="13" t="str">
+        <v>1.5364</v>
+      </c>
+      <c r="M40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="N40" s="13" t="str">
+        <v>1.5155000000000001</v>
+      </c>
+      <c r="N40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="O40" s="13" t="str">
+        <v>1.5367</v>
+      </c>
+      <c r="O40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="P40" s="13" t="str">
+        <v>1.4981</v>
+      </c>
+      <c r="P40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="Q40" s="13" t="str">
+        <v>2.5423</v>
+      </c>
+      <c r="Q40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="R40" s="13" t="str">
+        <v>3.3391000000000002</v>
+      </c>
+      <c r="R40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="S40" s="13" t="str">
+        <v>3.2677</v>
+      </c>
+      <c r="S40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="T40" s="13" t="str">
+        <v>4.4580000000000002</v>
+      </c>
+      <c r="T40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="U40" s="13" t="str">
+        <v>2.9392</v>
+      </c>
+      <c r="U40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="V40" s="13" t="str">
+        <v>2.9232999999999998</v>
+      </c>
+      <c r="V40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="W40" s="13" t="str">
+        <v>1.8746</v>
+      </c>
+      <c r="W40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="X40" s="13" t="str">
+        <v>1.8555999999999999</v>
+      </c>
+      <c r="X40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A40))</f>
-        <v/>
-      </c>
-      <c r="Y40" s="13" t="str">
+        <v>1.7986</v>
+      </c>
+      <c r="Y40" s="13">
         <f>IF($A40="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A40))</f>
-        <v/>
+        <v>2.484</v>
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="13" t="str">
+      <c r="A41" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",B$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="C41" s="13" t="str">
+        <v>3.22</v>
+      </c>
+      <c r="C41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",C$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="D41" s="13" t="str">
+        <v>1.3196231612</v>
+      </c>
+      <c r="D41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",D$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="E41" s="13" t="str">
+        <v>4.5060000000000002</v>
+      </c>
+      <c r="E41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",E$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="F41" s="13" t="str">
+        <v>1.8923000000000001</v>
+      </c>
+      <c r="F41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",F$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="G41" s="13" t="str">
+        <v>1.8381000000000001</v>
+      </c>
+      <c r="G41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",G$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="H41" s="13" t="str">
+        <v>3.7456999999999998</v>
+      </c>
+      <c r="H41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",H$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="I41" s="13" t="str">
+        <v>3.6652</v>
+      </c>
+      <c r="I41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",I$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="J41" s="13" t="str">
+        <v>2.4119000000000002</v>
+      </c>
+      <c r="J41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",J$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="K41" s="13" t="str">
+        <v>3.2107000000000001</v>
+      </c>
+      <c r="K41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",K$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="L41" s="13" t="str">
+        <v>3.1808000000000001</v>
+      </c>
+      <c r="L41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",L$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="M41" s="13" t="str">
+        <v>1.5364</v>
+      </c>
+      <c r="M41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",M$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="N41" s="13" t="str">
+        <v>1.5155000000000001</v>
+      </c>
+      <c r="N41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",N$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="O41" s="13" t="str">
+        <v>1.5367</v>
+      </c>
+      <c r="O41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",O$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="P41" s="13" t="str">
+        <v>1.4981</v>
+      </c>
+      <c r="P41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",P$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="Q41" s="13" t="str">
+        <v>2.5423</v>
+      </c>
+      <c r="Q41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",Q$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="R41" s="13" t="str">
+        <v>3.3391000000000002</v>
+      </c>
+      <c r="R41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",R$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="S41" s="13" t="str">
+        <v>3.2677</v>
+      </c>
+      <c r="S41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",S$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="T41" s="13" t="str">
+        <v>4.4580000000000002</v>
+      </c>
+      <c r="T41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",T$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="U41" s="13" t="str">
+        <v>2.9392</v>
+      </c>
+      <c r="U41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",U$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="V41" s="13" t="str">
+        <v>2.9232999999999998</v>
+      </c>
+      <c r="V41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",V$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="W41" s="13" t="str">
+        <v>1.8746</v>
+      </c>
+      <c r="W41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",W$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="X41" s="13" t="str">
+        <v>1.8555999999999999</v>
+      </c>
+      <c r="X41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",X$3,$A41))</f>
-        <v/>
-      </c>
-      <c r="Y41" s="13" t="str">
+        <v>1.7986</v>
+      </c>
+      <c r="Y41" s="13">
         <f>IF($A41="","",[1]!thsiFinD("ths_adjustment_nv_fund",Y$3,$A41))</f>
-        <v/>
+        <v>2.484</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -14857,7 +15123,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V61"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
     <col min="22" max="22" width="14.81640625" customWidth="1"/>
@@ -14865,7 +15131,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" customHeight="1">
       <c r="A1" s="56" t="s">
-        <v>63</v>
+        <v>207</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="56"/>
@@ -14891,81 +15157,81 @@
     </row>
     <row r="3" spans="1:22" ht="42" customHeight="1">
       <c r="B3" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="H3" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="K3" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="N3" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="Q3" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="13">
       <c r="A4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="H4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="K4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="N4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="Q4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="14">
@@ -17141,7 +17407,7 @@
         <v>-6.8693043624378003E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:21">
       <c r="A33" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A33="","",'实盘净值数据(iFinD公式)'!A33)</f>
         <v>46232</v>
@@ -17219,631 +17485,635 @@
         <v>-6.9548393453093604E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:21">
       <c r="A34" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A34="","",'实盘净值数据(iFinD公式)'!A34)</f>
         <v>46233</v>
       </c>
       <c r="B34" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A34="",'实盘净值数据(iFinD公式)'!$B34=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B34:$Y34/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A34-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v>0.75906478407377931</v>
+        <v>0.70197151091105148</v>
       </c>
       <c r="C34" s="16">
         <f t="shared" si="3"/>
-        <v>-4.1406369609475746E-5</v>
+        <v>-7.5253575785715565E-2</v>
       </c>
       <c r="D34" s="16">
         <f>IF(B34="","",B34/MAX(B$5:B34)-1)</f>
-        <v>-0.29379331177842616</v>
+        <v>-0.34691084826008267</v>
       </c>
       <c r="E34" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A34="",'实盘净值数据(iFinD公式)'!$B34=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B34:$Y34/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A34-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v>0.77642246795265424</v>
+        <v>0.71793541970282437</v>
       </c>
       <c r="F34" s="16">
         <f t="shared" si="4"/>
-        <v>-3.3075018034955939E-5</v>
+        <v>-7.5359480684621838E-2</v>
       </c>
       <c r="G34" s="16">
         <f>IF(E34="","",E34/MAX(E$5:E34)-1)</f>
-        <v>-0.29399251019223882</v>
+        <v>-0.34717527579407836</v>
       </c>
       <c r="H34" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A34="",'实盘净值数据(iFinD公式)'!$B34=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B34:$Y34/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A34-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v>0.80510863561266288</v>
+        <v>0.74787436802830576</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="5"/>
-        <v>-4.1406369609475746E-5</v>
+        <v>-7.1127338366311355E-2</v>
       </c>
       <c r="J34" s="16">
         <f>IF(H34="","",H34/MAX(H$5:H34)-1)</f>
-        <v>-0.2757904231939845</v>
+        <v>-0.32727366765642607</v>
       </c>
       <c r="K34" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A34="",'实盘净值数据(iFinD公式)'!$B34=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B34:$Y34/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A34-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v>0.98024749268353539</v>
+        <v>0.9761214913199201</v>
       </c>
       <c r="L34" s="16">
         <f t="shared" si="0"/>
-        <v>-2.2005707726258095E-5</v>
+        <v>-4.2310555638397362E-3</v>
       </c>
       <c r="M34" s="16">
         <f>IF(K34="","",K34/MAX(K$5:K34)-1)</f>
-        <v>-2.2949410622850719E-2</v>
+        <v>-2.7061955764950518E-2</v>
       </c>
       <c r="N34" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A34="",'实盘净值数据(iFinD公式)'!$B34=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B34:$Y34/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A34-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v>0.97824554543694497</v>
+        <v>0.97390321005734459</v>
       </c>
       <c r="O34" s="16">
         <f t="shared" si="1"/>
-        <v>-1.3732897000351407E-5</v>
+        <v>-4.4525731932946178E-3</v>
       </c>
       <c r="P34" s="16">
         <f>IF(N34="","",N34/MAX(N$5:N34)-1)</f>
-        <v>-2.4398470455744281E-2</v>
+        <v>-2.8729069309879618E-2</v>
       </c>
       <c r="Q34" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A34="",'实盘净值数据(iFinD公式)'!$B34=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B34:$Y34/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A34-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v>0.93857305927806578</v>
+        <v>0.92445284206535505</v>
       </c>
       <c r="R34" s="16">
         <f t="shared" si="2"/>
-        <v>-3.3075018034955939E-5</v>
+        <v>-1.507692274698258E-2</v>
       </c>
       <c r="S34" s="16">
         <f>IF(Q34="","",Q34/MAX(Q$5:Q34)-1)</f>
-        <v>-6.9579168156760796E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
-      <c r="A35" s="15" t="str">
+        <v>-8.3576740444807229E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A35="","",'实盘净值数据(iFinD公式)'!A35)</f>
-        <v/>
-      </c>
-      <c r="B35" s="13" t="str">
+        <v>46234</v>
+      </c>
+      <c r="B35" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A35="",'实盘净值数据(iFinD公式)'!$B35=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B35:$Y35/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A35-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v/>
-      </c>
-      <c r="C35" s="16" t="str">
+        <v>0.72624632001160483</v>
+      </c>
+      <c r="C35" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D35" s="16" t="str">
+        <v>3.4580903531324703E-2</v>
+      </c>
+      <c r="D35" s="16">
         <f>IF(B35="","",B35/MAX(B$5:B35)-1)</f>
-        <v/>
-      </c>
-      <c r="E35" s="13" t="str">
+        <v>-0.32432643530640981</v>
+      </c>
+      <c r="E35" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A35="",'实盘净值数据(iFinD公式)'!$B35=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B35:$Y35/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A35-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="F35" s="16" t="str">
+        <v>0.74282726366224527</v>
+      </c>
+      <c r="F35" s="16">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G35" s="16" t="str">
+        <v>3.4671424861200562E-2</v>
+      </c>
+      <c r="G35" s="16">
         <f>IF(E35="","",E35/MAX(E$5:E35)-1)</f>
-        <v/>
-      </c>
-      <c r="H35" s="13" t="str">
+        <v>-0.32454091242123884</v>
+      </c>
+      <c r="H35" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A35="",'实盘净值数据(iFinD公式)'!$B35=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B35:$Y35/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A35-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v/>
-      </c>
-      <c r="I35" s="16" t="str">
+        <v>0.77133249538722459</v>
+      </c>
+      <c r="I35" s="16">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J35" s="16" t="str">
+        <v>3.1366401045089587E-2</v>
+      </c>
+      <c r="J35" s="16">
         <f>IF(H35="","",H35/MAX(H$5:H35)-1)</f>
-        <v/>
-      </c>
-      <c r="K35" s="13" t="str">
+        <v>-0.30617266372254526</v>
+      </c>
+      <c r="K35" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A35="",'实盘净值数据(iFinD公式)'!$B35=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B35:$Y35/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A35-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="L35" s="16" t="str">
+        <v>0.97927214944896834</v>
+      </c>
+      <c r="L35" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M35" s="16" t="str">
+        <v>3.2277315447566401E-3</v>
+      </c>
+      <c r="M35" s="16">
         <f>IF(K35="","",K35/MAX(K$5:K35)-1)</f>
-        <v/>
-      </c>
-      <c r="N35" s="13" t="str">
+        <v>-2.3921572948479186E-2</v>
+      </c>
+      <c r="N35" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A35="",'实盘净值数据(iFinD公式)'!$B35=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B35:$Y35/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A35-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="O35" s="16" t="str">
+        <v>0.97719837247619623</v>
+      </c>
+      <c r="O35" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P35" s="16" t="str">
+        <v>3.3834598601001353E-3</v>
+      </c>
+      <c r="P35" s="16">
         <f>IF(N35="","",N35/MAX(N$5:N35)-1)</f>
-        <v/>
-      </c>
-      <c r="Q35" s="13" t="str">
+        <v>-2.5442813102607542E-2</v>
+      </c>
+      <c r="Q35" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A35="",'实盘净值数据(iFinD公式)'!$B35=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B35:$Y35/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A35-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="R35" s="16" t="str">
+        <v>0.93264826644668219</v>
+      </c>
+      <c r="R35" s="16">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S35" s="16" t="str">
+        <v>8.8651621893631738E-3</v>
+      </c>
+      <c r="S35" s="16">
         <f>IF(Q35="","",Q35/MAX(Q$5:Q35)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
-      <c r="A36" s="15" t="str">
+        <v>-7.5452499614745538E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A36="","",'实盘净值数据(iFinD公式)'!A36)</f>
-        <v/>
-      </c>
-      <c r="B36" s="13" t="str">
+        <v>46237</v>
+      </c>
+      <c r="B36" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A36="",'实盘净值数据(iFinD公式)'!$B36=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B36:$Y36/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A36-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v/>
-      </c>
-      <c r="C36" s="16" t="str">
+        <v>0.6962683081309522</v>
+      </c>
+      <c r="C36" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D36" s="16" t="str">
+        <v>-4.1278022421061822E-2</v>
+      </c>
+      <c r="D36" s="16">
         <f>IF(B36="","",B36/MAX(B$5:B36)-1)</f>
-        <v/>
-      </c>
-      <c r="E36" s="13" t="str">
+        <v>-0.35221690385915061</v>
+      </c>
+      <c r="E36" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A36="",'实盘净值数据(iFinD公式)'!$B36=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B36:$Y36/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A36-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="F36" s="16" t="str">
+        <v>0.71222410579163131</v>
+      </c>
+      <c r="F36" s="16">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G36" s="16" t="str">
+        <v>-4.1198215746331091E-2</v>
+      </c>
+      <c r="G36" s="16">
         <f>IF(E36="","",E36/MAX(E$5:E36)-1)</f>
-        <v/>
-      </c>
-      <c r="H36" s="13" t="str">
+        <v>-0.35236862163912863</v>
+      </c>
+      <c r="H36" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A36="",'实盘净值数据(iFinD公式)'!$B36=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B36:$Y36/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A36-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v/>
-      </c>
-      <c r="I36" s="16" t="str">
+        <v>0.73222495499610107</v>
+      </c>
+      <c r="I36" s="16">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J36" s="16" t="str">
+        <v>-5.0701274255910533E-2</v>
+      </c>
+      <c r="J36" s="16">
         <f>IF(H36="","",H36/MAX(H$5:H36)-1)</f>
-        <v/>
-      </c>
-      <c r="K36" s="13" t="str">
+        <v>-0.34135059378539634</v>
+      </c>
+      <c r="K36" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A36="",'实盘净值数据(iFinD公式)'!$B36=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B36:$Y36/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A36-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="L36" s="16" t="str">
+        <v>0.97645840479381407</v>
+      </c>
+      <c r="L36" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M36" s="16" t="str">
+        <v>-2.8733020302247336E-3</v>
+      </c>
+      <c r="M36" s="16">
         <f>IF(K36="","",K36/MAX(K$5:K36)-1)</f>
-        <v/>
-      </c>
-      <c r="N36" s="13" t="str">
+        <v>-2.672614107458493E-2</v>
+      </c>
+      <c r="N36" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A36="",'实盘净值数据(iFinD公式)'!$B36=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B36:$Y36/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A36-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="O36" s="16" t="str">
+        <v>0.97483599855662972</v>
+      </c>
+      <c r="O36" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P36" s="16" t="str">
+        <v>-2.4174967807000236E-3</v>
+      </c>
+      <c r="P36" s="16">
         <f>IF(N36="","",N36/MAX(N$5:N36)-1)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="13" t="str">
+        <v>-2.7798801964540099E-2</v>
+      </c>
+      <c r="Q36" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A36="",'实盘净值数据(iFinD公式)'!$B36=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B36:$Y36/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A36-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="R36" s="16" t="str">
+        <v>0.92408565948164412</v>
+      </c>
+      <c r="R36" s="16">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S36" s="16" t="str">
+        <v>-9.1809605754814561E-3</v>
+      </c>
+      <c r="S36" s="16">
         <f>IF(Q36="","",Q36/MAX(Q$5:Q36)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
-      <c r="A37" s="15" t="str">
+        <v>-8.3940733765942466E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A37="","",'实盘净值数据(iFinD公式)'!A37)</f>
-        <v/>
-      </c>
-      <c r="B37" s="13" t="str">
+        <v>46238</v>
+      </c>
+      <c r="B37" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A37="",'实盘净值数据(iFinD公式)'!$B37=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B37:$Y37/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A37-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v/>
-      </c>
-      <c r="C37" s="16" t="str">
+        <v>0.74614458366388403</v>
+      </c>
+      <c r="C37" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D37" s="16" t="str">
+        <v>7.1633700615813867E-2</v>
+      </c>
+      <c r="D37" s="16">
         <f>IF(B37="","",B37/MAX(B$5:B37)-1)</f>
-        <v/>
-      </c>
-      <c r="E37" s="13" t="str">
+        <v>-0.30581380348621212</v>
+      </c>
+      <c r="E37" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A37="",'实盘净值数据(iFinD公式)'!$B37=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B37:$Y37/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A37-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="F37" s="16" t="str">
+        <v>0.76336947663905597</v>
+      </c>
+      <c r="F37" s="16">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G37" s="16" t="str">
+        <v>7.1810783195237482E-2</v>
+      </c>
+      <c r="G37" s="16">
         <f>IF(E37="","",E37/MAX(E$5:E37)-1)</f>
-        <v/>
-      </c>
-      <c r="H37" s="13" t="str">
+        <v>-0.30586170513722333</v>
+      </c>
+      <c r="H37" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A37="",'实盘净值数据(iFinD公式)'!$B37=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B37:$Y37/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A37-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v/>
-      </c>
-      <c r="I37" s="16" t="str">
+        <v>0.77918745072942763</v>
+      </c>
+      <c r="I37" s="16">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J37" s="16" t="str">
+        <v>6.4136704728366745E-2</v>
+      </c>
+      <c r="J37" s="16">
         <f>IF(H37="","",H37/MAX(H$5:H37)-1)</f>
-        <v/>
-      </c>
-      <c r="K37" s="13" t="str">
+        <v>-0.29910699129949625</v>
+      </c>
+      <c r="K37" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A37="",'实盘净值数据(iFinD公式)'!$B37=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B37:$Y37/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A37-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="L37" s="16" t="str">
+        <v>0.9809307866654694</v>
+      </c>
+      <c r="L37" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M37" s="16" t="str">
+        <v>4.5802072568565944E-3</v>
+      </c>
+      <c r="M37" s="16">
         <f>IF(K37="","",K37/MAX(K$5:K37)-1)</f>
-        <v/>
-      </c>
-      <c r="N37" s="13" t="str">
+        <v>-2.2268345083025776E-2</v>
+      </c>
+      <c r="N37" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A37="",'实盘净值数据(iFinD公式)'!$B37=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B37:$Y37/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A37-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="O37" s="16" t="str">
+        <v>0.97968557339554074</v>
+      </c>
+      <c r="O37" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P37" s="16" t="str">
+        <v>4.9747596991611687E-3</v>
+      </c>
+      <c r="P37" s="16">
         <f>IF(N37="","",N37/MAX(N$5:N37)-1)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="13" t="str">
+        <v>-2.296233462507713E-2</v>
+      </c>
+      <c r="Q37" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A37="",'实盘净值数据(iFinD公式)'!$B37=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B37:$Y37/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A37-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="R37" s="16" t="str">
+        <v>0.93652463834702993</v>
+      </c>
+      <c r="R37" s="16">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S37" s="16" t="str">
+        <v>1.3460850450123019E-2</v>
+      </c>
+      <c r="S37" s="16">
         <f>IF(Q37="","",Q37/MAX(Q$5:Q37)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
-      <c r="A38" s="15" t="str">
+        <v>-7.1609796979716256E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A38="","",'实盘净值数据(iFinD公式)'!A38)</f>
-        <v/>
-      </c>
-      <c r="B38" s="13" t="str">
+        <v>46239</v>
+      </c>
+      <c r="B38" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A38="",'实盘净值数据(iFinD公式)'!$B38=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B38:$Y38/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A38-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v/>
-      </c>
-      <c r="C38" s="16" t="str">
+        <v>0.77896150349312188</v>
+      </c>
+      <c r="C38" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D38" s="16" t="str">
+        <v>4.3981984923207484E-2</v>
+      </c>
+      <c r="D38" s="16">
         <f>IF(B38="","",B38/MAX(B$5:B38)-1)</f>
-        <v/>
-      </c>
-      <c r="E38" s="13" t="str">
+        <v>-0.27528211665724389</v>
+      </c>
+      <c r="E38" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A38="",'实盘净值数据(iFinD公式)'!$B38=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B38:$Y38/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A38-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="F38" s="16" t="str">
+        <v>0.79692340056760913</v>
+      </c>
+      <c r="F38" s="16">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G38" s="16" t="str">
+        <v>4.3955024343236282E-2</v>
+      </c>
+      <c r="G38" s="16">
         <f>IF(E38="","",E38/MAX(E$5:E38)-1)</f>
-        <v/>
-      </c>
-      <c r="H38" s="13" t="str">
+        <v>-0.27535083948895744</v>
+      </c>
+      <c r="H38" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A38="",'实盘净值数据(iFinD公式)'!$B38=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B38:$Y38/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A38-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v/>
-      </c>
-      <c r="I38" s="16" t="str">
+        <v>0.81627637308703827</v>
+      </c>
+      <c r="I38" s="16">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J38" s="16" t="str">
+        <v>4.7599486263401936E-2</v>
+      </c>
+      <c r="J38" s="16">
         <f>IF(H38="","",H38/MAX(H$5:H38)-1)</f>
-        <v/>
-      </c>
-      <c r="K38" s="13" t="str">
+        <v>-0.26574484415974209</v>
+      </c>
+      <c r="K38" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A38="",'实盘净值数据(iFinD公式)'!$B38=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B38:$Y38/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A38-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="L38" s="16" t="str">
+        <v>0.98575511215025358</v>
+      </c>
+      <c r="L38" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M38" s="16" t="str">
+        <v>4.9181099730633004E-3</v>
+      </c>
+      <c r="M38" s="16">
         <f>IF(K38="","",K38/MAX(K$5:K38)-1)</f>
-        <v/>
-      </c>
-      <c r="N38" s="13" t="str">
+        <v>-1.7459753279999046E-2</v>
+      </c>
+      <c r="N38" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A38="",'实盘净值数据(iFinD公式)'!$B38=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B38:$Y38/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A38-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="O38" s="16" t="str">
+        <v>0.98435681211622128</v>
+      </c>
+      <c r="O38" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P38" s="16" t="str">
+        <v>4.7680999368913124E-3</v>
+      </c>
+      <c r="P38" s="16">
         <f>IF(N38="","",N38/MAX(N$5:N38)-1)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="13" t="str">
+        <v>-1.8303721394462569E-2</v>
+      </c>
+      <c r="Q38" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A38="",'实盘净值数据(iFinD公式)'!$B38=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B38:$Y38/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A38-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="R38" s="16" t="str">
+        <v>0.94971573113282171</v>
+      </c>
+      <c r="R38" s="16">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S38" s="16" t="str">
+        <v>1.4085152964127046E-2</v>
+      </c>
+      <c r="S38" s="16">
         <f>IF(Q38="","",Q38/MAX(Q$5:Q38)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
-      <c r="A39" s="15" t="str">
+        <v>-5.8533278959778445E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A39="","",'实盘净值数据(iFinD公式)'!A39)</f>
-        <v/>
-      </c>
-      <c r="B39" s="13" t="str">
+        <v>46240</v>
+      </c>
+      <c r="B39" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A39="",'实盘净值数据(iFinD公式)'!$B39=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B39:$Y39/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A39-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v/>
-      </c>
-      <c r="C39" s="16" t="str">
+        <v>0.79001227829138299</v>
+      </c>
+      <c r="C39" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D39" s="16" t="str">
+        <v>1.4186548049814673E-2</v>
+      </c>
+      <c r="D39" s="16">
         <f>IF(B39="","",B39/MAX(B$5:B39)-1)</f>
-        <v/>
-      </c>
-      <c r="E39" s="13" t="str">
+        <v>-0.26500087158264185</v>
+      </c>
+      <c r="E39" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A39="",'实盘净值数据(iFinD公式)'!$B39=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B39:$Y39/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A39-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="F39" s="16" t="str">
+        <v>0.80826511012075786</v>
+      </c>
+      <c r="F39" s="16">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G39" s="16" t="str">
+        <v>1.4231869142091513E-2</v>
+      </c>
+      <c r="G39" s="16">
         <f>IF(E39="","",E39/MAX(E$5:E39)-1)</f>
-        <v/>
-      </c>
-      <c r="H39" s="13" t="str">
+        <v>-0.26503772746263787</v>
+      </c>
+      <c r="H39" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A39="",'实盘净值数据(iFinD公式)'!$B39=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B39:$Y39/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A39-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v/>
-      </c>
-      <c r="I39" s="16" t="str">
+        <v>0.82647704725758364</v>
+      </c>
+      <c r="I39" s="16">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J39" s="16" t="str">
+        <v>1.249659368672873E-2</v>
+      </c>
+      <c r="J39" s="16">
         <f>IF(H39="","",H39/MAX(H$5:H39)-1)</f>
-        <v/>
-      </c>
-      <c r="K39" s="13" t="str">
+        <v>-0.25656915581482065</v>
+      </c>
+      <c r="K39" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A39="",'实盘净值数据(iFinD公式)'!$B39=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B39:$Y39/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A39-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="L39" s="16" t="str">
+        <v>0.98807991531029082</v>
+      </c>
+      <c r="L39" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M39" s="16" t="str">
+        <v>2.358398279026952E-3</v>
+      </c>
+      <c r="M39" s="16">
         <f>IF(K39="","",K39/MAX(K$5:K39)-1)</f>
-        <v/>
-      </c>
-      <c r="N39" s="13" t="str">
+        <v>-1.5142532053059821E-2</v>
+      </c>
+      <c r="N39" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A39="",'实盘净值数据(iFinD公式)'!$B39=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B39:$Y39/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A39-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="O39" s="16" t="str">
+        <v>0.98673128064354332</v>
+      </c>
+      <c r="O39" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P39" s="16" t="str">
+        <v>2.4122030732101063E-3</v>
+      </c>
+      <c r="P39" s="16">
         <f>IF(N39="","",N39/MAX(N$5:N39)-1)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="13" t="str">
+        <v>-1.5935670614251385E-2</v>
+      </c>
+      <c r="Q39" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A39="",'实盘净值数据(iFinD公式)'!$B39=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B39:$Y39/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A39-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="R39" s="16" t="str">
+        <v>0.95513401394071007</v>
+      </c>
+      <c r="R39" s="16">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S39" s="16" t="str">
+        <v>5.7051627453041931E-3</v>
+      </c>
+      <c r="S39" s="16">
         <f>IF(Q39="","",Q39/MAX(Q$5:Q39)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
-      <c r="A40" s="15" t="str">
+        <v>-5.3162058096956066E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A40="","",'实盘净值数据(iFinD公式)'!A40)</f>
-        <v/>
-      </c>
-      <c r="B40" s="13" t="str">
+        <v>46241</v>
+      </c>
+      <c r="B40" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A40="",'实盘净值数据(iFinD公式)'!$B40=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B40:$Y40/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A40-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v/>
-      </c>
-      <c r="C40" s="16" t="str">
+        <v>0.81131379383137059</v>
+      </c>
+      <c r="C40" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D40" s="16" t="str">
+        <v>2.6963524650601478E-2</v>
+      </c>
+      <c r="D40" s="16">
         <f>IF(B40="","",B40/MAX(B$5:B40)-1)</f>
-        <v/>
-      </c>
-      <c r="E40" s="13" t="str">
+        <v>-0.24518270446538981</v>
+      </c>
+      <c r="E40" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A40="",'实盘净值数据(iFinD公式)'!$B40=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B40:$Y40/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A40-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="F40" s="16" t="str">
+        <v>0.83008467669236141</v>
+      </c>
+      <c r="F40" s="16">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G40" s="16" t="str">
+        <v>2.699555665386022E-2</v>
+      </c>
+      <c r="G40" s="16">
         <f>IF(E40="","",E40/MAX(E$5:E40)-1)</f>
-        <v/>
-      </c>
-      <c r="H40" s="13" t="str">
+        <v>-0.24519701179590569</v>
+      </c>
+      <c r="H40" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A40="",'实盘净值数据(iFinD公式)'!$B40=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B40:$Y40/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A40-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v/>
-      </c>
-      <c r="I40" s="16" t="str">
+        <v>0.84783459383647197</v>
+      </c>
+      <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J40" s="16" t="str">
+        <v>2.5841669347935303E-2</v>
+      </c>
+      <c r="J40" s="16">
         <f>IF(H40="","",H40/MAX(H$5:H40)-1)</f>
-        <v/>
-      </c>
-      <c r="K40" s="13" t="str">
+        <v>-0.23735766175633088</v>
+      </c>
+      <c r="K40" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A40="",'实盘净值数据(iFinD公式)'!$B40=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B40:$Y40/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A40-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="L40" s="16" t="str">
+        <v>0.99118243223928182</v>
+      </c>
+      <c r="L40" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M40" s="16" t="str">
+        <v>3.139945343405337E-3</v>
+      </c>
+      <c r="M40" s="16">
         <f>IF(K40="","",K40/MAX(K$5:K40)-1)</f>
-        <v/>
-      </c>
-      <c r="N40" s="13" t="str">
+        <v>-1.2050133432661703E-2</v>
+      </c>
+      <c r="N40" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A40="",'实盘净值数据(iFinD公式)'!$B40=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B40:$Y40/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A40-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="O40" s="16" t="str">
+        <v>0.98991772635449637</v>
+      </c>
+      <c r="O40" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P40" s="16" t="str">
+        <v>3.2292943108835903E-3</v>
+      </c>
+      <c r="P40" s="16">
         <f>IF(N40="","",N40/MAX(N$5:N40)-1)</f>
-        <v/>
-      </c>
-      <c r="Q40" s="13" t="str">
+        <v>-1.2757837273822514E-2</v>
+      </c>
+      <c r="Q40" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A40="",'实盘净值数据(iFinD公式)'!$B40=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B40:$Y40/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A40-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="R40" s="16" t="str">
+        <v>0.96277386059938297</v>
+      </c>
+      <c r="R40" s="16">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S40" s="16" t="str">
+        <v>7.9987169833395377E-3</v>
+      </c>
+      <c r="S40" s="16">
         <f>IF(Q40="","",Q40/MAX(Q$5:Q40)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
-      <c r="A41" s="15" t="str">
+        <v>-4.5588569370585863E-2</v>
+      </c>
+      <c r="U40">
+        <f>E40/E35-1</f>
+        <v>0.11746662689778575</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" s="15">
         <f>IF('实盘净值数据(iFinD公式)'!A41="","",'实盘净值数据(iFinD公式)'!A41)</f>
-        <v/>
-      </c>
-      <c r="B41" s="13" t="str">
+        <v>46244</v>
+      </c>
+      <c r="B41" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A41="",'实盘净值数据(iFinD公式)'!$B41=""),"",分期持仓明细!$AB$17*SUMPRODUCT(分期持仓明细!$B$17:$Y$17,'实盘净值数据(iFinD公式)'!$B41:$Y41/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$4)^(('实盘净值数据(iFinD公式)'!$A41-'实盘净值数据(iFinD公式)'!$A$6)/365))</f>
-        <v/>
-      </c>
-      <c r="C41" s="16" t="str">
+        <v>0.81121594075829673</v>
+      </c>
+      <c r="C41" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D41" s="16" t="str">
+        <v>-1.2061063649826398E-4</v>
+      </c>
+      <c r="D41" s="16">
         <f>IF(B41="","",B41/MAX(B$5:B41)-1)</f>
-        <v/>
-      </c>
-      <c r="E41" s="13" t="str">
+        <v>-0.2452737434598441</v>
+      </c>
+      <c r="E41" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A41="",'实盘净值数据(iFinD公式)'!$B41=""),"",分期持仓明细!$AB$18*SUMPRODUCT(分期持仓明细!$B$18:$Y$18,'实盘净值数据(iFinD公式)'!$B41:$Y41/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$5)^(('实盘净值数据(iFinD公式)'!$A41-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="F41" s="16" t="str">
+        <v>0.83000523901410417</v>
+      </c>
+      <c r="F41" s="16">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G41" s="16" t="str">
+        <v>-9.5698282943534885E-5</v>
+      </c>
+      <c r="G41" s="16">
         <f>IF(E41="","",E41/MAX(E$5:E41)-1)</f>
-        <v/>
-      </c>
-      <c r="H41" s="13" t="str">
+        <v>-0.24526924514583748</v>
+      </c>
+      <c r="H41" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A41="",'实盘净值数据(iFinD公式)'!$B41=""),"",分期持仓明细!$AB$19*SUMPRODUCT(分期持仓明细!$B$19:$Y$19,'实盘净值数据(iFinD公式)'!$B41:$Y41/'实盘净值数据(iFinD公式)'!$B$20:$Y$20)*(1-实盘持仓配置!$Z$6)^(('实盘净值数据(iFinD公式)'!$A41-'实盘净值数据(iFinD公式)'!$A$7)/365))</f>
-        <v/>
-      </c>
-      <c r="I41" s="16" t="str">
+        <v>0.84773216402641249</v>
+      </c>
+      <c r="I41" s="16">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J41" s="16" t="str">
+        <v>-1.2081343554992685E-4</v>
+      </c>
+      <c r="J41" s="16">
         <f>IF(H41="","",H41/MAX(H$5:H41)-1)</f>
-        <v/>
-      </c>
-      <c r="K41" s="13" t="str">
+        <v>-0.23744979919730991</v>
+      </c>
+      <c r="K41" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A41="",'实盘净值数据(iFinD公式)'!$B41=""),"",分期持仓明细!$AB$20*SUMPRODUCT(分期持仓明细!$B$20:$Y$20,'实盘净值数据(iFinD公式)'!$B41:$Y41/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$7)^(('实盘净值数据(iFinD公式)'!$A41-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="L41" s="16" t="str">
+        <v>0.99111988587101385</v>
+      </c>
+      <c r="L41" s="16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M41" s="16" t="str">
+        <v>-6.3102781318158385E-5</v>
+      </c>
+      <c r="M41" s="16">
         <f>IF(K41="","",K41/MAX(K$5:K41)-1)</f>
-        <v/>
-      </c>
-      <c r="N41" s="13" t="str">
+        <v>-1.2112475817044999E-2</v>
+      </c>
+      <c r="N41" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A41="",'实盘净值数据(iFinD公式)'!$B41=""),"",分期持仓明细!$AB$21*SUMPRODUCT(分期持仓明细!$B$21:$Y$21,'实盘净值数据(iFinD公式)'!$B41:$Y41/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$8)^(('实盘净值数据(iFinD公式)'!$A41-'实盘净值数据(iFinD公式)'!$A$5)/365))</f>
-        <v/>
-      </c>
-      <c r="O41" s="16" t="str">
+        <v>0.9898798291506663</v>
+      </c>
+      <c r="O41" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P41" s="16" t="str">
+        <v>-3.8283185381127183E-5</v>
+      </c>
+      <c r="P41" s="16">
         <f>IF(N41="","",N41/MAX(N$5:N41)-1)</f>
-        <v/>
-      </c>
-      <c r="Q41" s="13" t="str">
+        <v>-1.2795632048554273E-2</v>
+      </c>
+      <c r="Q41" s="13">
         <f>IF(OR('实盘净值数据(iFinD公式)'!$A41="",'实盘净值数据(iFinD公式)'!$B41=""),"",分期持仓明细!$AB$22*SUMPRODUCT(分期持仓明细!$B$22:$Y$22,'实盘净值数据(iFinD公式)'!$B41:$Y41/'实盘净值数据(iFinD公式)'!$B$25:$Y$25)*(1-实盘持仓配置!$Z$9)^(('实盘净值数据(iFinD公式)'!$A41-'实盘净值数据(iFinD公式)'!$A$8)/365))</f>
-        <v/>
-      </c>
-      <c r="R41" s="16" t="str">
+        <v>0.96268377880038403</v>
+      </c>
+      <c r="R41" s="16">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S41" s="16" t="str">
+        <v>-9.3564857424399683E-5</v>
+      </c>
+      <c r="S41" s="16">
         <f>IF(Q41="","",Q41/MAX(Q$5:Q41)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
+        <v>-4.5677868740016891E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" s="15" t="str">
         <f>IF('实盘净值数据(iFinD公式)'!A42="","",'实盘净值数据(iFinD公式)'!A42)</f>
         <v/>
@@ -17921,7 +18191,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:21">
       <c r="A43" s="15" t="str">
         <f>IF('实盘净值数据(iFinD公式)'!A43="","",'实盘净值数据(iFinD公式)'!A43)</f>
         <v/>
@@ -17999,7 +18269,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:21">
       <c r="A44" s="15" t="str">
         <f>IF('实盘净值数据(iFinD公式)'!A44="","",'实盘净值数据(iFinD公式)'!A44)</f>
         <v/>
@@ -18077,7 +18347,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:21">
       <c r="A45" s="15" t="str">
         <f>IF('实盘净值数据(iFinD公式)'!A45="","",'实盘净值数据(iFinD公式)'!A45)</f>
         <v/>
@@ -18155,7 +18425,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:21">
       <c r="A46" s="15" t="str">
         <f>IF('实盘净值数据(iFinD公式)'!A46="","",'实盘净值数据(iFinD公式)'!A46)</f>
         <v/>
@@ -18233,7 +18503,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:21">
       <c r="A47" s="15" t="str">
         <f>IF('实盘净值数据(iFinD公式)'!A47="","",'实盘净值数据(iFinD公式)'!A47)</f>
         <v/>
@@ -18311,7 +18581,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:21">
       <c r="A48" s="15" t="str">
         <f>IF('实盘净值数据(iFinD公式)'!A48="","",'实盘净值数据(iFinD公式)'!A48)</f>
         <v/>
@@ -19249,7 +19519,7 @@
     </row>
     <row r="61" spans="1:19" ht="14.25" customHeight="1">
       <c r="A61" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -19258,16 +19528,16 @@
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB22"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="37.54296875" customWidth="1"/>
+    <col min="1" max="1" width="37.453125" customWidth="1"/>
     <col min="2" max="6" width="9.26953125" customWidth="1"/>
     <col min="7" max="7" width="24.26953125" customWidth="1"/>
     <col min="8" max="8" width="16.26953125" customWidth="1"/>
@@ -19278,7 +19548,7 @@
   <sheetData>
     <row r="1" spans="1:28">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="14.5">
@@ -19286,73 +19556,73 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="G2" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="H2" s="19" t="s">
         <v>81</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>82</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="M2" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="P2" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="Q2" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="R2" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="S2" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="T2" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="T2" s="19" t="s">
+      <c r="U2" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="V2" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="W2" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="X2" s="19" t="s">
         <v>96</v>
-      </c>
-      <c r="X2" s="19" t="s">
-        <v>97</v>
       </c>
       <c r="Y2" t="s">
         <v>62</v>
@@ -19361,10 +19631,10 @@
         <v>25</v>
       </c>
       <c r="AA2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB2" s="19" t="s">
         <v>98</v>
-      </c>
-      <c r="AB2" s="19" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="14">
@@ -19372,81 +19642,81 @@
         <v>28</v>
       </c>
       <c r="B3" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="E3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="F3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="G3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="H3" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="I3" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="J3" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="K3" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="L3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="M3" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="N3" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="O3" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="P3" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="Q3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="Q3" s="20" t="s">
+      <c r="R3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="R3" s="20" t="s">
+      <c r="S3" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="S3" s="20" t="s">
+      <c r="T3" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="T3" s="20" t="s">
+      <c r="U3" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="U3" s="20" t="s">
+      <c r="V3" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="V3" s="20" t="s">
+      <c r="W3" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="W3" s="20" t="s">
+      <c r="X3" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="X3" s="20" t="s">
+      <c r="Y3" s="20" t="s">
         <v>122</v>
-      </c>
-      <c r="Y3" s="20" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="14.5">
       <c r="A5" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="21">
         <f>实盘持仓配置!B4</f>
@@ -19553,7 +19823,7 @@
     </row>
     <row r="6" spans="1:28" ht="14.5">
       <c r="A6" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="21">
         <f>实盘持仓配置!B5</f>
@@ -19660,7 +19930,7 @@
     </row>
     <row r="7" spans="1:28" ht="14.5">
       <c r="A7" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" s="21">
         <f>实盘持仓配置!B6</f>
@@ -19767,7 +20037,7 @@
     </row>
     <row r="8" spans="1:28" ht="14.5">
       <c r="A8" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" s="21">
         <f>实盘持仓配置!B7</f>
@@ -19874,7 +20144,7 @@
     </row>
     <row r="9" spans="1:28" ht="14.5">
       <c r="A9" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9">
         <f>B$8*'实盘净值数据(iFinD公式)'!B$13/'实盘净值数据(iFinD公式)'!B$8/$AB$9</f>
@@ -19986,7 +20256,7 @@
     </row>
     <row r="10" spans="1:28" ht="14.5">
       <c r="A10" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" s="21">
         <f>实盘持仓配置!B8</f>
@@ -20093,7 +20363,7 @@
     </row>
     <row r="11" spans="1:28" ht="14.5">
       <c r="A11" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11">
         <f>B$10*'实盘净值数据(iFinD公式)'!B$13/'实盘净值数据(iFinD公式)'!B$5/$AB$11</f>
@@ -20205,7 +20475,7 @@
     </row>
     <row r="12" spans="1:28" ht="14.5">
       <c r="A12" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="21">
         <f>实盘持仓配置!B9</f>
@@ -20312,7 +20582,7 @@
     </row>
     <row r="13" spans="1:28" ht="14.5">
       <c r="A13" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13">
         <f>B$12*'实盘净值数据(iFinD公式)'!B$13/'实盘净值数据(iFinD公式)'!B$8/$AB$13</f>
@@ -20424,7 +20694,7 @@
     </row>
     <row r="14" spans="1:28" ht="14.5">
       <c r="A14" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14">
         <v>5.1392931664740599E-2</v>
@@ -20512,7 +20782,7 @@
     </row>
     <row r="15" spans="1:28" ht="14.5">
       <c r="A15" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B15">
         <v>4.9150896792573798E-2</v>
@@ -20600,7 +20870,7 @@
     </row>
     <row r="16" spans="1:28" ht="14.5">
       <c r="A16" s="23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16">
         <v>0.103481083555403</v>
@@ -20688,7 +20958,7 @@
     </row>
     <row r="17" spans="1:28" ht="14.5">
       <c r="A17" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -20776,7 +21046,7 @@
     </row>
     <row r="18" spans="1:28" ht="14.5">
       <c r="A18" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -20864,7 +21134,7 @@
     </row>
     <row r="19" spans="1:28" ht="14.5">
       <c r="A19" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -20952,7 +21222,7 @@
     </row>
     <row r="20" spans="1:28" ht="14">
       <c r="A20" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B20">
         <v>5.1393000000000001E-2</v>
@@ -21040,7 +21310,7 @@
     </row>
     <row r="21" spans="1:28" ht="14">
       <c r="A21" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21">
         <v>4.9151E-2</v>
@@ -21128,7 +21398,7 @@
     </row>
     <row r="22" spans="1:28" ht="14">
       <c r="A22" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22">
         <v>0.103481</v>
@@ -21224,11 +21494,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G35"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="2.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
     <col min="4" max="4" width="22.453125" customWidth="1"/>
     <col min="5" max="5" width="17.36328125" customWidth="1"/>
     <col min="6" max="6" width="19.26953125" customWidth="1"/>
@@ -21237,256 +21507,250 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" customHeight="1">
-      <c r="B2" s="60" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="B2" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="2:7" ht="14.25" customHeight="1">
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="58" t="str">
         <f>"买入持有 · 已扣年化费率 "&amp;TEXT(实盘持仓配置!$Z$4,"0.0%")&amp;"（折每日计入净值）"</f>
         <v>买入持有 · 已扣年化费率 1.5%（折每日计入净值）</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62" t="str">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59" t="str">
         <f>"净值日期："&amp;TEXT(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),"yyyy-mm-dd")</f>
-        <v>净值日期：2026-07-30</v>
-      </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+        <v>净值日期：2026-08-10</v>
+      </c>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="5" spans="2:7" ht="14">
-      <c r="B5" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
     </row>
     <row r="6" spans="2:7" ht="13">
       <c r="B6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="27.75" customHeight="1">
       <c r="B7" s="27">
         <f>LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)</f>
-        <v>0.75906478407377931</v>
+        <v>0.81121594075829673</v>
       </c>
       <c r="C7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59))/1-1</f>
-        <v>-0.24093521592622069</v>
+        <v>-0.18878405924170327</v>
       </c>
       <c r="D7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$C$5:$C$59),1))-1</f>
-        <v>-0.90768609008209711</v>
+        <v>-0.76463404960033299</v>
       </c>
       <c r="E7" s="29">
         <f>STDEV(实盘组合净值!$C$5:$C$59)*SQRT(说明!$C$17)</f>
-        <v>0.70062207030377999</v>
+        <v>0.71911895415688043</v>
       </c>
       <c r="F7" s="28">
         <f>MIN(实盘组合净值!$D$5:$D$59)</f>
-        <v>-0.29379331177842616</v>
+        <v>-0.35221690385915061</v>
       </c>
       <c r="G7" s="30">
         <f>(((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$C$5:$C$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$C$5:$C$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$C$5:$C$59)*SQRT(说明!$C$17)))</f>
-        <v>-1.295543101701802</v>
+        <v>-1.0632928602150613</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="14">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
     </row>
     <row r="10" spans="2:7" ht="13.5" customHeight="1">
       <c r="B10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="F10" s="62"/>
+      <c r="G10" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="22.5" customHeight="1">
       <c r="B11" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59))/(1)-1,"")</f>
-        <v>-0.24093521592622069</v>
+        <v>-0.18878405924170327</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/(1))^(说明!$C$17/COUNT(实盘组合净值!$C$5:$C$59))-1,"")</f>
-        <v>-0.90768609008209711</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="57"/>
+        <v>-0.76463404960033299</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="61"/>
       <c r="G11" s="32">
         <f>MIN(实盘组合净值!$D$5:$D$59)</f>
-        <v>-0.29379331177842616</v>
+        <v>-0.35221690385915061</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="22.5" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59))/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1))-1,"")</f>
-        <v>-0.24093521592622069</v>
+        <v>-0.18878405924170327</v>
       </c>
       <c r="D12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(DATE(2026,1,1))),1))-1,"")</f>
-        <v>-0.89179450004226191</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="F12" s="57"/>
+        <v>-0.74549082766040731</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="34">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),ROW(实盘组合净值!$B$5:$B$59)))-(LOOKUP(2,1/(实盘组合净值!$D$5:$D$59=0),ROW(实盘组合净值!$D$5:$D$59))),"")</f>
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="22.5" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1))-1,"")</f>
-        <v>-0.24093521592622069</v>
+        <v>-0.18878405924170327</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3))),1))-1,"")</f>
-        <v>-0.89179450004226191</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="57"/>
+        <v>-0.74549082766040731</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="35">
         <f>COUNTIF(实盘组合净值!$C$5:$C$59,"&gt;0")/MAX(COUNT(实盘组合净值!$C$5:$C$59),1)</f>
-        <v>0.35714285714285715</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="22.5" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1))-1,"")</f>
-        <v>-0.24093521592622069</v>
+        <v>-0.18878405924170327</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6))),1))-1,"")</f>
-        <v>-0.89179450004226191</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="57"/>
+        <v>-0.74549082766040731</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="61"/>
       <c r="G14" s="32">
         <f>STDEV(实盘组合净值!$C$5:$C$59)*SQRT(说明!$C$17)</f>
-        <v>0.70062207030377999</v>
+        <v>0.71911895415688043</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="22.5" customHeight="1">
       <c r="B15" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1))-1,"")</f>
-        <v>-0.24093521592622069</v>
+        <v>-0.18878405924170327</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$B$5:$B$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12))),1))-1,"")</f>
-        <v>-0.89179450004226191</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="57"/>
+        <v>-0.74549082766040731</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="61"/>
       <c r="G15" s="36">
         <f>(((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$C$5:$C$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$C$5:$C$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$C$5:$C$59)*SQRT(说明!$C$17)))</f>
-        <v>-1.295543101701802</v>
+        <v>-1.0632928602150613</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="22.5" customHeight="1">
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
-      <c r="E16" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="F16" s="57"/>
+      <c r="E16" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="61"/>
       <c r="G16" s="36">
         <f>IFERROR(((LOOKUP(2,1/(实盘组合净值!$B$5:$B$59&lt;&gt;""),实盘组合净值!$B$5:$B$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$C$5:$C$59),1))-1)/ABS(MIN(实盘组合净值!$D$5:$D$59)),"")</f>
-        <v>-3.0895396651053049</v>
+        <v>-2.1709180939995587</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14">
-      <c r="B18" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="35" spans="2:2" ht="14.25" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="B18:G18"/>
@@ -21495,6 +21759,12 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21506,11 +21776,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G35"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="2.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.453125" customWidth="1"/>
     <col min="5" max="5" width="17.36328125" customWidth="1"/>
     <col min="6" max="6" width="19.26953125" customWidth="1"/>
@@ -21519,256 +21789,250 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" customHeight="1">
-      <c r="B2" s="60" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="B2" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="2:7" ht="14.25" customHeight="1">
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="58" t="str">
         <f>"买入持有 · 已扣年化费率 "&amp;TEXT(实盘持仓配置!$Z$5,"0.0%")&amp;"（折每日计入净值）"</f>
         <v>买入持有 · 已扣年化费率 1.2%（折每日计入净值）</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62" t="str">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59" t="str">
         <f>"净值日期："&amp;TEXT(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),"yyyy-mm-dd")</f>
-        <v>净值日期：2026-07-30</v>
-      </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+        <v>净值日期：2026-08-10</v>
+      </c>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="5" spans="2:7" ht="14">
-      <c r="B5" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
     </row>
     <row r="6" spans="2:7" ht="13">
       <c r="B6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="27.75" customHeight="1">
       <c r="B7" s="27">
         <f>LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)</f>
-        <v>0.77642246795265424</v>
+        <v>0.83000523901410417</v>
       </c>
       <c r="C7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59))/1-1</f>
-        <v>-0.22357753204734576</v>
+        <v>-0.16999476098589583</v>
       </c>
       <c r="D7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$F$5:$F$59),1))-1</f>
-        <v>-0.87897152904318543</v>
+        <v>-0.71421239965525074</v>
       </c>
       <c r="E7" s="29">
         <f>STDEV(实盘组合净值!$F$5:$F$59)*SQRT(说明!$C$17)</f>
-        <v>0.69469008977241742</v>
+        <v>0.71312743462307415</v>
       </c>
       <c r="F7" s="28">
         <f>MIN(实盘组合净值!$G$5:$G$59)</f>
-        <v>-0.29399251019223882</v>
+        <v>-0.35236862163912863</v>
       </c>
       <c r="G7" s="30">
         <f>(((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$F$5:$F$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$F$5:$F$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$F$5:$F$59)*SQRT(说明!$C$17)))</f>
-        <v>-1.2652714382770873</v>
+        <v>-1.0015214181638519</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="14">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
     </row>
     <row r="10" spans="2:7" ht="13.5" customHeight="1">
       <c r="B10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="F10" s="62"/>
+      <c r="G10" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="22.5" customHeight="1">
       <c r="B11" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59))/(1)-1,"")</f>
-        <v>-0.22357753204734576</v>
+        <v>-0.16999476098589583</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/(1))^(说明!$C$17/COUNT(实盘组合净值!$F$5:$F$59))-1,"")</f>
-        <v>-0.87897152904318543</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="57"/>
+        <v>-0.71421239965525074</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="61"/>
       <c r="G11" s="32">
         <f>MIN(实盘组合净值!$G$5:$G$59)</f>
-        <v>-0.29399251019223882</v>
+        <v>-0.35236862163912863</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="22.5" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59))/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1))-1,"")</f>
-        <v>-0.22357753204734576</v>
+        <v>-0.16999476098589583</v>
       </c>
       <c r="D12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(DATE(2026,1,1))),1))-1,"")</f>
-        <v>-0.87014521375717768</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="F12" s="57"/>
+        <v>-0.70437244464766435</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="34">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),ROW(实盘组合净值!$E$5:$E$59)))-(LOOKUP(2,1/(实盘组合净值!$G$5:$G$59=0),ROW(实盘组合净值!$G$5:$G$59))),"")</f>
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="22.5" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1))-1,"")</f>
-        <v>-0.22357753204734576</v>
+        <v>-0.16999476098589583</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3))),1))-1,"")</f>
-        <v>-0.87014521375717768</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="57"/>
+        <v>-0.70437244464766435</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="35">
         <f>COUNTIF(实盘组合净值!$F$5:$F$59,"&gt;0")/MAX(COUNT(实盘组合净值!$F$5:$F$59),1)</f>
-        <v>0.37931034482758619</v>
+        <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="22.5" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1))-1,"")</f>
-        <v>-0.22357753204734576</v>
+        <v>-0.16999476098589583</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6))),1))-1,"")</f>
-        <v>-0.87014521375717768</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="57"/>
+        <v>-0.70437244464766435</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="61"/>
       <c r="G14" s="32">
         <f>STDEV(实盘组合净值!$F$5:$F$59)*SQRT(说明!$C$17)</f>
-        <v>0.69469008977241742</v>
+        <v>0.71312743462307415</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="22.5" customHeight="1">
       <c r="B15" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1))-1,"")</f>
-        <v>-0.22357753204734576</v>
+        <v>-0.16999476098589583</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$E$5:$E$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12))),1))-1,"")</f>
-        <v>-0.87014521375717768</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="57"/>
+        <v>-0.70437244464766435</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="61"/>
       <c r="G15" s="36">
         <f>(((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$F$5:$F$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$F$5:$F$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$F$5:$F$59)*SQRT(说明!$C$17)))</f>
-        <v>-1.2652714382770873</v>
+        <v>-1.0015214181638519</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="22.5" customHeight="1">
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
-      <c r="E16" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="F16" s="57"/>
+      <c r="E16" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="61"/>
       <c r="G16" s="36">
         <f>IFERROR(((LOOKUP(2,1/(实盘组合净值!$E$5:$E$59&lt;&gt;""),实盘组合净值!$E$5:$E$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$F$5:$F$59),1))-1)/ABS(MIN(实盘组合净值!$G$5:$G$59)),"")</f>
-        <v>-2.9897752445068568</v>
+        <v>-2.026889898234745</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14">
-      <c r="B18" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="35" spans="2:2" ht="14.25" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="B18:G18"/>
@@ -21777,6 +22041,12 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21788,11 +22058,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G35"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="2.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
     <col min="4" max="4" width="27.26953125" customWidth="1"/>
     <col min="5" max="5" width="17.36328125" customWidth="1"/>
     <col min="6" max="6" width="19.26953125" customWidth="1"/>
@@ -21801,256 +22071,250 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" customHeight="1">
-      <c r="B2" s="60" t="s">
-        <v>166</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="B2" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="2:7" ht="14.25" customHeight="1">
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="58" t="str">
         <f>"买入持有 · 已扣年化费率 "&amp;TEXT(实盘持仓配置!$Z$6,"0.0%")&amp;"（折每日计入净值）"</f>
         <v>买入持有 · 已扣年化费率 1.5%（折每日计入净值）</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62" t="str">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59" t="str">
         <f>"净值日期："&amp;TEXT(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),"yyyy-mm-dd")</f>
-        <v>净值日期：2026-07-30</v>
-      </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+        <v>净值日期：2026-08-10</v>
+      </c>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="5" spans="2:7" ht="14">
-      <c r="B5" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
     </row>
     <row r="6" spans="2:7" ht="13">
       <c r="B6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="27.75" customHeight="1">
       <c r="B7" s="27">
         <f>LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)</f>
-        <v>0.80510863561266288</v>
+        <v>0.84773216402641249</v>
       </c>
       <c r="C7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59))/1-1</f>
-        <v>-0.19489136438733712</v>
+        <v>-0.15226783597358751</v>
       </c>
       <c r="D7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$I$5:$I$59),1))-1</f>
-        <v>-0.85672275068042769</v>
+        <v>-0.69141808452015519</v>
       </c>
       <c r="E7" s="29">
         <f>STDEV(实盘组合净值!$I$5:$I$59)*SQRT(说明!$C$17)</f>
-        <v>0.69989824802430012</v>
+        <v>0.71278422201905134</v>
       </c>
       <c r="F7" s="28">
         <f>MIN(实盘组合净值!$J$5:$J$59)</f>
-        <v>-0.2757904231939845</v>
+        <v>-0.34135059378539634</v>
       </c>
       <c r="G7" s="30">
         <f>(((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$I$5:$I$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$I$5:$I$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$I$5:$I$59)*SQRT(说明!$C$17)))</f>
-        <v>-1.2240675742492824</v>
+        <v>-0.97002439610914248</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="14">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
     </row>
     <row r="10" spans="2:7" ht="13.5" customHeight="1">
       <c r="B10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="F10" s="62"/>
+      <c r="G10" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="22.5" customHeight="1">
       <c r="B11" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59))/(1)-1,"")</f>
-        <v>-0.19489136438733712</v>
+        <v>-0.15226783597358751</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/(1))^(说明!$C$17/COUNT(实盘组合净值!$I$5:$I$59))-1,"")</f>
-        <v>-0.85672275068042769</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="57"/>
+        <v>-0.69141808452015519</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="61"/>
       <c r="G11" s="32">
         <f>MIN(实盘组合净值!$J$5:$J$59)</f>
-        <v>-0.2757904231939845</v>
+        <v>-0.34135059378539634</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="22.5" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59))/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1))-1,"")</f>
-        <v>-0.19489136438733712</v>
+        <v>-0.15226783597358751</v>
       </c>
       <c r="D12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(DATE(2026,1,1))),1))-1,"")</f>
-        <v>-0.82599588792222389</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="F12" s="57"/>
+        <v>-0.66055230433682555</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="34">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),ROW(实盘组合净值!$H$5:$H$59)))-(LOOKUP(2,1/(实盘组合净值!$J$5:$J$59=0),ROW(实盘组合净值!$J$5:$J$59))),"")</f>
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="22.5" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1))-1,"")</f>
-        <v>-0.19489136438733712</v>
+        <v>-0.15226783597358751</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3))),1))-1,"")</f>
-        <v>-0.82599588792222389</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="57"/>
+        <v>-0.66055230433682555</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="35">
         <f>COUNTIF(实盘组合净值!$I$5:$I$59,"&gt;0")/MAX(COUNT(实盘组合净值!$I$5:$I$59),1)</f>
-        <v>0.40740740740740738</v>
+        <v>0.47058823529411764</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="22.5" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1))-1,"")</f>
-        <v>-0.19489136438733712</v>
+        <v>-0.15226783597358751</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6))),1))-1,"")</f>
-        <v>-0.82599588792222389</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="57"/>
+        <v>-0.66055230433682555</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="61"/>
       <c r="G14" s="32">
         <f>STDEV(实盘组合净值!$I$5:$I$59)*SQRT(说明!$C$17)</f>
-        <v>0.69989824802430012</v>
+        <v>0.71278422201905134</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="22.5" customHeight="1">
       <c r="B15" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1))-1,"")</f>
-        <v>-0.19489136438733712</v>
+        <v>-0.15226783597358751</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$H$5:$H$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12))),1))-1,"")</f>
-        <v>-0.82599588792222389</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="57"/>
+        <v>-0.66055230433682555</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="61"/>
       <c r="G15" s="36">
         <f>(((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$I$5:$I$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$I$5:$I$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$I$5:$I$59)*SQRT(说明!$C$17)))</f>
-        <v>-1.2240675742492824</v>
+        <v>-0.97002439610914248</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="22.5" customHeight="1">
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
-      <c r="E16" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="F16" s="57"/>
+      <c r="E16" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="61"/>
       <c r="G16" s="36">
         <f>IFERROR(((LOOKUP(2,1/(实盘组合净值!$H$5:$H$59&lt;&gt;""),实盘组合净值!$H$5:$H$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$I$5:$I$59),1))-1)/ABS(MIN(实盘组合净值!$J$5:$J$59)),"")</f>
-        <v>-3.1064267597059709</v>
+        <v>-2.0255364927088504</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14">
-      <c r="B18" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="35" spans="2:2" ht="14.25" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="B18:G18"/>
@@ -22059,6 +22323,12 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22070,269 +22340,263 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G35"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="2.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
     <col min="4" max="4" width="18.90625" customWidth="1"/>
     <col min="5" max="5" width="21.26953125" customWidth="1"/>
-    <col min="6" max="6" width="16.54296875" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
+    <col min="7" max="7" width="19.453125" customWidth="1"/>
     <col min="8" max="8" width="2.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" customHeight="1">
-      <c r="B2" s="60" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="B2" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="2:7" ht="14.25" customHeight="1">
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="58" t="str">
         <f>"买入持有 · 已扣年化费率 "&amp;TEXT(实盘持仓配置!$Z$7,"0.0%")&amp;"（折每日计入净值）"</f>
         <v>买入持有 · 已扣年化费率 0.8%（折每日计入净值）</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62" t="str">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59" t="str">
         <f>"净值日期："&amp;TEXT(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),"yyyy-mm-dd")</f>
-        <v>净值日期：2026-07-30</v>
-      </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+        <v>净值日期：2026-08-10</v>
+      </c>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="5" spans="2:7" ht="14">
-      <c r="B5" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
     </row>
     <row r="6" spans="2:7" ht="13">
       <c r="B6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="27.75" customHeight="1">
       <c r="B7" s="27">
         <f>LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)</f>
-        <v>0.98024749268353539</v>
+        <v>0.99111988587101385</v>
       </c>
       <c r="C7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59))/1-1</f>
-        <v>-1.9752507316464607E-2</v>
+        <v>-8.8801141289861496E-3</v>
       </c>
       <c r="D7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$L$5:$L$59),1))-1</f>
-        <v>-0.16946921497738465</v>
+        <v>-6.331824826040533E-2</v>
       </c>
       <c r="E7" s="29">
         <f>STDEV(实盘组合净值!$L$5:$L$59)*SQRT(说明!$C$17)</f>
-        <v>5.6562904996294787E-2</v>
+        <v>5.77127122303564E-2</v>
       </c>
       <c r="F7" s="28">
         <f>MIN(实盘组合净值!$M$5:$M$59)</f>
-        <v>-2.6258222837610368E-2</v>
+        <v>-2.7061955764950518E-2</v>
       </c>
       <c r="G7" s="30">
         <f>(((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$L$5:$L$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$L$5:$L$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$L$5:$L$59)*SQRT(说明!$C$17)))</f>
-        <v>-2.9961193645992177</v>
+        <v>-1.0971282723236921</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="14">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
     </row>
     <row r="10" spans="2:7" ht="13.5" customHeight="1">
       <c r="B10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="F10" s="62"/>
+      <c r="G10" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="22.5" customHeight="1">
       <c r="B11" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59))/(1)-1,"")</f>
-        <v>-1.9752507316464607E-2</v>
+        <v>-8.8801141289861496E-3</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/(1))^(说明!$C$17/COUNT(实盘组合净值!$L$5:$L$59))-1,"")</f>
-        <v>-0.16946921497738465</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="57"/>
+        <v>-6.331824826040533E-2</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="61"/>
       <c r="G11" s="32">
         <f>MIN(实盘组合净值!$M$5:$M$59)</f>
-        <v>-2.6258222837610368E-2</v>
+        <v>-2.7061955764950518E-2</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="22.5" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59))/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1))-1,"")</f>
-        <v>-1.9752507316464607E-2</v>
+        <v>-8.8801141289861496E-3</v>
       </c>
       <c r="D12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(DATE(2026,1,1))),1))-1,"")</f>
-        <v>-0.14864967997815792</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="F12" s="57"/>
+        <v>-5.6670994860237078E-2</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="34">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),ROW(实盘组合净值!$K$5:$K$59)))-(LOOKUP(2,1/(实盘组合净值!$M$5:$M$59=0),ROW(实盘组合净值!$M$5:$M$59))),"")</f>
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="22.5" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1))-1,"")</f>
-        <v>-1.9752507316464607E-2</v>
+        <v>-8.8801141289861496E-3</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3))),1))-1,"")</f>
-        <v>-0.14864967997815792</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="57"/>
+        <v>-5.6670994860237078E-2</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="35">
         <f>COUNTIF(实盘组合净值!$L$5:$L$59,"&gt;0")/MAX(COUNT(实盘组合净值!$L$5:$L$59),1)</f>
-        <v>0.34615384615384615</v>
+        <v>0.42424242424242425</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="22.5" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1))-1,"")</f>
-        <v>-1.9752507316464607E-2</v>
+        <v>-8.8801141289861496E-3</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6))),1))-1,"")</f>
-        <v>-0.14864967997815792</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="57"/>
+        <v>-5.6670994860237078E-2</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="61"/>
       <c r="G14" s="32">
         <f>STDEV(实盘组合净值!$L$5:$L$59)*SQRT(说明!$C$17)</f>
-        <v>5.6562904996294787E-2</v>
+        <v>5.77127122303564E-2</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="22.5" customHeight="1">
       <c r="B15" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1))-1,"")</f>
-        <v>-1.9752507316464607E-2</v>
+        <v>-8.8801141289861496E-3</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$K$5:$K$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12))),1))-1,"")</f>
-        <v>-0.14864967997815792</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="57"/>
+        <v>-5.6670994860237078E-2</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="61"/>
       <c r="G15" s="36">
         <f>(((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$L$5:$L$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$L$5:$L$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$L$5:$L$59)*SQRT(说明!$C$17)))</f>
-        <v>-2.9961193645992177</v>
+        <v>-1.0971282723236921</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="22.5" customHeight="1">
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
-      <c r="E16" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="F16" s="57"/>
+      <c r="E16" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="61"/>
       <c r="G16" s="36">
         <f>IFERROR(((LOOKUP(2,1/(实盘组合净值!$K$5:$K$59&lt;&gt;""),实盘组合净值!$K$5:$K$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$L$5:$L$59),1))-1)/ABS(MIN(实盘组合净值!$M$5:$M$59)),"")</f>
-        <v>-6.4539483888699918</v>
+        <v>-2.3397513768170595</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14">
-      <c r="B18" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="35" spans="2:2" ht="14.25" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="B18:G18"/>
@@ -22341,6 +22605,12 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22352,269 +22622,263 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G35"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="2.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
     <col min="4" max="4" width="20.08984375" customWidth="1"/>
     <col min="5" max="5" width="17.36328125" customWidth="1"/>
-    <col min="6" max="6" width="16.54296875" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
     <col min="7" max="7" width="19.08984375" customWidth="1"/>
     <col min="8" max="8" width="2.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" customHeight="1">
-      <c r="B2" s="60" t="s">
-        <v>168</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="B2" s="57" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="2:7" ht="14.25" customHeight="1">
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="58" t="str">
         <f>"买入持有 · 已扣年化费率 "&amp;TEXT(实盘持仓配置!$Z$8,"0.0%")&amp;"（折每日计入净值）"</f>
         <v>买入持有 · 已扣年化费率 0.5%（折每日计入净值）</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62" t="str">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59" t="str">
         <f>"净值日期："&amp;TEXT(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),"yyyy-mm-dd")</f>
-        <v>净值日期：2026-07-30</v>
-      </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+        <v>净值日期：2026-08-10</v>
+      </c>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="5" spans="2:7" ht="14">
-      <c r="B5" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
     </row>
     <row r="6" spans="2:7" ht="13">
       <c r="B6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="27.75" customHeight="1">
       <c r="B7" s="27">
         <f>LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)</f>
-        <v>0.97824554543694497</v>
+        <v>0.9898798291506663</v>
       </c>
       <c r="C7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59))/1-1</f>
-        <v>-2.1754454563055026E-2</v>
+        <v>-1.0120170849333698E-2</v>
       </c>
       <c r="D7" s="28">
         <f>(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$O$5:$O$59),1))-1</f>
-        <v>-0.16768217262501683</v>
+        <v>-6.6091317098222913E-2</v>
       </c>
       <c r="E7" s="29">
         <f>STDEV(实盘组合净值!$O$5:$O$59)*SQRT(说明!$C$17)</f>
-        <v>5.615148876961288E-2</v>
+        <v>5.7568197593900201E-2</v>
       </c>
       <c r="F7" s="28">
         <f>MIN(实盘组合净值!$P$5:$P$59)</f>
-        <v>-2.7120539144761091E-2</v>
+        <v>-2.8729069309879618E-2</v>
       </c>
       <c r="G7" s="30">
         <f>(((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$O$5:$O$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$O$5:$O$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$O$5:$O$59)*SQRT(说明!$C$17)))</f>
-        <v>-2.9862462474149085</v>
+        <v>-1.1480525682677583</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="14">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
     </row>
     <row r="10" spans="2:7" ht="13.5" customHeight="1">
       <c r="B10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="F10" s="62"/>
+      <c r="G10" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="22.5" customHeight="1">
       <c r="B11" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59))/(1)-1,"")</f>
-        <v>-2.1754454563055026E-2</v>
+        <v>-1.0120170849333698E-2</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/(1))^(说明!$C$17/COUNT(实盘组合净值!$O$5:$O$59))-1,"")</f>
-        <v>-0.16768217262501683</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="57"/>
+        <v>-6.6091317098222913E-2</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="61"/>
       <c r="G11" s="32">
         <f>MIN(实盘组合净值!$P$5:$P$59)</f>
-        <v>-2.7120539144761091E-2</v>
+        <v>-2.8729069309879618E-2</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="22.5" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59))/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1))-1,"")</f>
-        <v>-2.1754454563055026E-2</v>
+        <v>-1.0120170849333698E-2</v>
       </c>
       <c r="D12" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/(IFERROR(LOOKUP(DATE(2026,1,1),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(DATE(2026,1,1))),1))-1,"")</f>
-        <v>-0.16257441822615293</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="F12" s="57"/>
+        <v>-6.4363842608737065E-2</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="34">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),ROW(实盘组合净值!$N$5:$N$59)))-(LOOKUP(2,1/(实盘组合净值!$P$5:$P$59=0),ROW(实盘组合净值!$P$5:$P$59))),"")</f>
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="22.5" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1))-1,"")</f>
-        <v>-2.1754454563055026E-2</v>
+        <v>-1.0120170849333698E-2</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-3))),1))-1,"")</f>
-        <v>-0.16257441822615293</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="57"/>
+        <v>-6.4363842608737065E-2</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="35">
         <f>COUNTIF(实盘组合净值!$O$5:$O$59,"&gt;0")/MAX(COUNT(实盘组合净值!$O$5:$O$59),1)</f>
-        <v>0.37931034482758619</v>
+        <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="22.5" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1))-1,"")</f>
-        <v>-2.1754454563055026E-2</v>
+        <v>-1.0120170849333698E-2</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-6))),1))-1,"")</f>
-        <v>-0.16257441822615293</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="57"/>
+        <v>-6.4363842608737065E-2</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="61"/>
       <c r="G14" s="32">
         <f>STDEV(实盘组合净值!$O$5:$O$59)*SQRT(说明!$C$17)</f>
-        <v>5.615148876961288E-2</v>
+        <v>5.7568197593900201E-2</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="22.5" customHeight="1">
       <c r="B15" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59))/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1))-1,"")</f>
-        <v>-2.1754454563055026E-2</v>
+        <v>-1.0120170849333698E-2</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/(IFERROR(LOOKUP(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12),实盘组合净值!$A$5:$A$59,实盘组合净值!$N$5:$N$59),1)))^(说明!$C$17/MAX(COUNTIF(实盘组合净值!$A$5:$A$59,"&gt;="&amp;(EDATE(LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$A$5:$A$59),-12))),1))-1,"")</f>
-        <v>-0.16257441822615293</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="57"/>
+        <v>-6.4363842608737065E-2</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="61"/>
       <c r="G15" s="36">
         <f>(((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$O$5:$O$59),1))-1)-说明!$C$16)/IF((STDEV(实盘组合净值!$O$5:$O$59)*SQRT(说明!$C$17))=0,"",(STDEV(实盘组合净值!$O$5:$O$59)*SQRT(说明!$C$17)))</f>
-        <v>-2.9862462474149085</v>
+        <v>-1.1480525682677583</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="22.5" customHeight="1">
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
-      <c r="E16" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="F16" s="57"/>
+      <c r="E16" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="61"/>
       <c r="G16" s="36">
         <f>IFERROR(((LOOKUP(2,1/(实盘组合净值!$N$5:$N$59&lt;&gt;""),实盘组合净值!$N$5:$N$59)/1)^(说明!$C$17/MAX(COUNT(实盘组合净值!$O$5:$O$59),1))-1)/ABS(MIN(实盘组合净值!$P$5:$P$59)),"")</f>
-        <v>-6.1828480521711242</v>
+        <v>-2.3005032423899237</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14">
-      <c r="B18" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="35" spans="2:2" ht="14.25" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="B18:G18"/>
@@ -22623,6 +22887,12 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
